--- a/neetcode_150_tracker.xlsx
+++ b/neetcode_150_tracker.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="202">
   <si>
     <t xml:space="preserve">#</t>
   </si>
@@ -633,13 +633,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="166" formatCode="General"/>
-    <numFmt numFmtId="167" formatCode="0%"/>
+    <numFmt numFmtId="165" formatCode="d&quot;. &quot;mmm&quot;. &quot;yyyy"/>
+    <numFmt numFmtId="166" formatCode="d&quot;. &quot;mmmm\ yyyy"/>
+    <numFmt numFmtId="167" formatCode="General"/>
+    <numFmt numFmtId="168" formatCode="0%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -675,6 +676,11 @@
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="0"/>
     </font>
     <font>
       <b val="true"/>
@@ -786,7 +792,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -796,10 +802,26 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -812,7 +834,15 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -823,15 +853,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -839,11 +869,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1144,3962 +1178,3979 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="3" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="4" width="19.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="15.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="3" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="n">
+      <c r="A2" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6" t="str">
+      <c r="E2" s="10"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="10" t="str">
         <f aca="false">IF(J2="","",J2+14)</f>
         <v/>
       </c>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="8"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6" t="str">
+      <c r="E3" s="10"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="10" t="str">
         <f aca="false">IF(J3="","",J3+14)</f>
         <v/>
       </c>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="8"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6" t="str">
+      <c r="E4" s="10"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="10" t="str">
         <f aca="false">IF(J4="","",J4+14)</f>
         <v/>
       </c>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6" t="str">
+      <c r="D5" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="10"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="10" t="str">
         <f aca="false">IF(J5="","",J5+14)</f>
         <v/>
       </c>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6" t="str">
+      <c r="D6" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="10"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="10" t="str">
         <f aca="false">IF(J6="","",J6+14)</f>
         <v/>
       </c>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6" t="str">
+      <c r="D7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="10" t="str">
         <f aca="false">IF(J7="","",J7+14)</f>
         <v/>
       </c>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6" t="str">
+      <c r="D8" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="10"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="10" t="str">
         <f aca="false">IF(J8="","",J8+14)</f>
         <v/>
       </c>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6" t="str">
+      <c r="D9" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="10"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="10" t="str">
         <f aca="false">IF(J9="","",J9+14)</f>
         <v/>
       </c>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6" t="str">
+      <c r="D10" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="10"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="10" t="str">
         <f aca="false">IF(J10="","",J10+14)</f>
         <v/>
       </c>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="8"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="6"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6" t="str">
+      <c r="E11" s="10"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="10" t="str">
         <f aca="false">IF(J11="","",J11+14)</f>
         <v/>
       </c>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6" t="str">
+      <c r="D12" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="10"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="10" t="str">
         <f aca="false">IF(J12="","",J12+14)</f>
         <v/>
       </c>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="8"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6" t="str">
+      <c r="D13" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="10"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="10" t="str">
         <f aca="false">IF(J13="","",J13+14)</f>
         <v/>
       </c>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="8"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="6"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6" t="str">
+      <c r="D14" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="10"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="10" t="str">
         <f aca="false">IF(J14="","",J14+14)</f>
         <v/>
       </c>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="8"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="6"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6" t="str">
+      <c r="E15" s="10"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="10" t="str">
         <f aca="false">IF(J15="","",J15+14)</f>
         <v/>
       </c>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="8"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="6"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6" t="str">
+      <c r="E16" s="10"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="10" t="str">
         <f aca="false">IF(J16="","",J16+14)</f>
         <v/>
       </c>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E17" s="6"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6" t="str">
+      <c r="D17" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="10"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="10" t="str">
         <f aca="false">IF(J17="","",J17+14)</f>
         <v/>
       </c>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E18" s="6"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6" t="str">
+      <c r="D18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="10"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="10" t="str">
         <f aca="false">IF(J18="","",J18+14)</f>
         <v/>
       </c>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E19" s="6"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6" t="str">
+      <c r="D19" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="10"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="10" t="str">
         <f aca="false">IF(J19="","",J19+14)</f>
         <v/>
       </c>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="8"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="4" t="s">
+      <c r="A20" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E20" s="6"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6" t="str">
+      <c r="E20" s="10"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="10" t="str">
         <f aca="false">IF(J20="","",J20+14)</f>
         <v/>
       </c>
-      <c r="L20" s="4"/>
-      <c r="M20" s="4"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="8"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E21" s="6"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6" t="str">
+      <c r="E21" s="10"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="10" t="str">
         <f aca="false">IF(J21="","",J21+14)</f>
         <v/>
       </c>
-      <c r="L21" s="4"/>
-      <c r="M21" s="4"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="8"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="n">
+      <c r="A22" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E22" s="6"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6" t="str">
+      <c r="E22" s="10"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="10" t="str">
         <f aca="false">IF(J22="","",J22+14)</f>
         <v/>
       </c>
-      <c r="L22" s="4"/>
-      <c r="M22" s="4"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="8"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D23" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E23" s="6"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6" t="str">
+      <c r="D23" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="10"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="10" t="str">
         <f aca="false">IF(J23="","",J23+14)</f>
         <v/>
       </c>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="8"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="n">
+      <c r="A24" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D24" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E24" s="6"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6" t="str">
+      <c r="D24" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="10"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="10" t="str">
         <f aca="false">IF(J24="","",J24+14)</f>
         <v/>
       </c>
-      <c r="L24" s="4"/>
-      <c r="M24" s="4"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="8"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="n">
+      <c r="A25" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D25" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E25" s="6"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6" t="str">
+      <c r="D25" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="10"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="10" t="str">
         <f aca="false">IF(J25="","",J25+14)</f>
         <v/>
       </c>
-      <c r="L25" s="4"/>
-      <c r="M25" s="4"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="8"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="n">
+      <c r="A26" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D26" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E26" s="6"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6" t="str">
+      <c r="D26" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="10"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="10" t="str">
         <f aca="false">IF(J26="","",J26+14)</f>
         <v/>
       </c>
-      <c r="L26" s="4"/>
-      <c r="M26" s="4"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="8"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D27" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E27" s="6"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6" t="str">
+      <c r="D27" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" s="10"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="10" t="str">
         <f aca="false">IF(J27="","",J27+14)</f>
         <v/>
       </c>
-      <c r="L27" s="4"/>
-      <c r="M27" s="4"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="8"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="n">
+      <c r="A28" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E28" s="6"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6" t="str">
+      <c r="E28" s="10"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="10" t="str">
         <f aca="false">IF(J28="","",J28+14)</f>
         <v/>
       </c>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="8"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="n">
+      <c r="A29" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E29" s="6"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6" t="str">
+      <c r="E29" s="10"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="10" t="str">
         <f aca="false">IF(J29="","",J29+14)</f>
         <v/>
       </c>
-      <c r="L29" s="4"/>
-      <c r="M29" s="4"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="8"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="n">
+      <c r="A30" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D30" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="6"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6" t="str">
+      <c r="D30" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="10"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="10" t="str">
         <f aca="false">IF(J30="","",J30+14)</f>
         <v/>
       </c>
-      <c r="L30" s="4"/>
-      <c r="M30" s="4"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="8"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="n">
+      <c r="A31" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D31" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E31" s="6"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6" t="str">
+      <c r="D31" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" s="10"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="10" t="str">
         <f aca="false">IF(J31="","",J31+14)</f>
         <v/>
       </c>
-      <c r="L31" s="4"/>
-      <c r="M31" s="4"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="8"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="n">
+      <c r="A32" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D32" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E32" s="6"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="6" t="str">
+      <c r="D32" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="10"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="10" t="str">
         <f aca="false">IF(J32="","",J32+14)</f>
         <v/>
       </c>
-      <c r="L32" s="4"/>
-      <c r="M32" s="4"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="8"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="n">
+      <c r="A33" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D33" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E33" s="6"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6" t="str">
+      <c r="D33" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" s="10"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="12"/>
+      <c r="K33" s="10" t="str">
         <f aca="false">IF(J33="","",J33+14)</f>
         <v/>
       </c>
-      <c r="L33" s="4"/>
-      <c r="M33" s="4"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="8"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="n">
+      <c r="A34" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D34" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E34" s="6"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="6" t="str">
+      <c r="D34" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E34" s="10"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="10" t="str">
         <f aca="false">IF(J34="","",J34+14)</f>
         <v/>
       </c>
-      <c r="L34" s="4"/>
-      <c r="M34" s="4"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="8"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="n">
+      <c r="A35" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E35" s="6"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="6" t="str">
+      <c r="E35" s="10"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="12"/>
+      <c r="K35" s="10" t="str">
         <f aca="false">IF(J35="","",J35+14)</f>
         <v/>
       </c>
-      <c r="L35" s="4"/>
-      <c r="M35" s="4"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="8"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="n">
+      <c r="A36" s="8" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E36" s="6"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="6" t="str">
+      <c r="E36" s="10"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="10" t="str">
         <f aca="false">IF(J36="","",J36+14)</f>
         <v/>
       </c>
-      <c r="L36" s="4"/>
-      <c r="M36" s="4"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="8"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="n">
+      <c r="A37" s="8" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D37" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E37" s="6"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="6" t="str">
+      <c r="E37" s="10"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="12"/>
+      <c r="K37" s="10" t="str">
         <f aca="false">IF(J37="","",J37+14)</f>
         <v/>
       </c>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="8"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="n">
+      <c r="A38" s="8" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="D38" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E38" s="6"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6" t="str">
+      <c r="D38" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38" s="10"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="12"/>
+      <c r="K38" s="10" t="str">
         <f aca="false">IF(J38="","",J38+14)</f>
         <v/>
       </c>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="8"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="n">
+      <c r="A39" s="8" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="D39" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="6"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6" t="str">
+      <c r="D39" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="10"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="12"/>
+      <c r="K39" s="10" t="str">
         <f aca="false">IF(J39="","",J39+14)</f>
         <v/>
       </c>
-      <c r="L39" s="4"/>
-      <c r="M39" s="4"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="8"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="n">
+      <c r="A40" s="8" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="D40" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E40" s="6"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="6"/>
-      <c r="K40" s="6" t="str">
+      <c r="D40" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" s="10"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="12"/>
+      <c r="K40" s="10" t="str">
         <f aca="false">IF(J40="","",J40+14)</f>
         <v/>
       </c>
-      <c r="L40" s="4"/>
-      <c r="M40" s="4"/>
+      <c r="L40" s="11"/>
+      <c r="M40" s="8"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="n">
+      <c r="A41" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D41" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E41" s="6"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="6"/>
-      <c r="K41" s="6" t="str">
+      <c r="D41" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E41" s="10"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="12"/>
+      <c r="K41" s="10" t="str">
         <f aca="false">IF(J41="","",J41+14)</f>
         <v/>
       </c>
-      <c r="L41" s="4"/>
-      <c r="M41" s="4"/>
+      <c r="L41" s="11"/>
+      <c r="M41" s="8"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="n">
+      <c r="A42" s="8" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D42" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E42" s="6"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="6"/>
-      <c r="K42" s="6" t="str">
+      <c r="E42" s="10"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+      <c r="I42" s="11"/>
+      <c r="J42" s="12"/>
+      <c r="K42" s="10" t="str">
         <f aca="false">IF(J42="","",J42+14)</f>
         <v/>
       </c>
-      <c r="L42" s="4"/>
-      <c r="M42" s="4"/>
+      <c r="L42" s="11"/>
+      <c r="M42" s="8"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="n">
+      <c r="A43" s="8" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="D43" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E43" s="6"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="6"/>
-      <c r="K43" s="6" t="str">
+      <c r="D43" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E43" s="10"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="12"/>
+      <c r="K43" s="10" t="str">
         <f aca="false">IF(J43="","",J43+14)</f>
         <v/>
       </c>
-      <c r="L43" s="4"/>
-      <c r="M43" s="4"/>
+      <c r="L43" s="11"/>
+      <c r="M43" s="8"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="n">
+      <c r="A44" s="8" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D44" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E44" s="6"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="6"/>
-      <c r="K44" s="6" t="str">
+      <c r="D44" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E44" s="10"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="12"/>
+      <c r="K44" s="10" t="str">
         <f aca="false">IF(J44="","",J44+14)</f>
         <v/>
       </c>
-      <c r="L44" s="4"/>
-      <c r="M44" s="4"/>
+      <c r="L44" s="11"/>
+      <c r="M44" s="8"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="n">
+      <c r="A45" s="8" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="D45" s="8" t="s">
+      <c r="D45" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E45" s="6"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
-      <c r="J45" s="6"/>
-      <c r="K45" s="6" t="str">
+      <c r="E45" s="10"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="12"/>
+      <c r="K45" s="10" t="str">
         <f aca="false">IF(J45="","",J45+14)</f>
         <v/>
       </c>
-      <c r="L45" s="4"/>
-      <c r="M45" s="4"/>
+      <c r="L45" s="11"/>
+      <c r="M45" s="8"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4" t="n">
+      <c r="A46" s="8" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D46" s="8" t="s">
+      <c r="D46" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E46" s="6"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
-      <c r="J46" s="6"/>
-      <c r="K46" s="6" t="str">
+      <c r="E46" s="10"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="12"/>
+      <c r="K46" s="10" t="str">
         <f aca="false">IF(J46="","",J46+14)</f>
         <v/>
       </c>
-      <c r="L46" s="4"/>
-      <c r="M46" s="4"/>
+      <c r="L46" s="11"/>
+      <c r="M46" s="8"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="n">
+      <c r="A47" s="8" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="D47" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E47" s="6"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-      <c r="J47" s="6"/>
-      <c r="K47" s="6" t="str">
+      <c r="E47" s="10"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="11"/>
+      <c r="J47" s="12"/>
+      <c r="K47" s="10" t="str">
         <f aca="false">IF(J47="","",J47+14)</f>
         <v/>
       </c>
-      <c r="L47" s="4"/>
-      <c r="M47" s="4"/>
+      <c r="L47" s="11"/>
+      <c r="M47" s="8"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="n">
+      <c r="A48" s="8" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D48" s="5" t="s">
+      <c r="D48" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E48" s="6"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="6"/>
-      <c r="K48" s="6" t="str">
+      <c r="E48" s="10"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8"/>
+      <c r="I48" s="11"/>
+      <c r="J48" s="12"/>
+      <c r="K48" s="10" t="str">
         <f aca="false">IF(J48="","",J48+14)</f>
         <v/>
       </c>
-      <c r="L48" s="4"/>
-      <c r="M48" s="4"/>
+      <c r="L48" s="11"/>
+      <c r="M48" s="8"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="n">
+      <c r="A49" s="8" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="C49" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D49" s="5" t="s">
+      <c r="D49" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E49" s="6"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="6"/>
-      <c r="K49" s="6" t="str">
+      <c r="E49" s="10"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="8"/>
+      <c r="H49" s="8"/>
+      <c r="I49" s="11"/>
+      <c r="J49" s="12"/>
+      <c r="K49" s="10" t="str">
         <f aca="false">IF(J49="","",J49+14)</f>
         <v/>
       </c>
-      <c r="L49" s="4"/>
-      <c r="M49" s="4"/>
+      <c r="L49" s="11"/>
+      <c r="M49" s="8"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="n">
+      <c r="A50" s="8" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C50" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="D50" s="5" t="s">
+      <c r="D50" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E50" s="6"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="6"/>
-      <c r="K50" s="6" t="str">
+      <c r="E50" s="10"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="8"/>
+      <c r="I50" s="11"/>
+      <c r="J50" s="12"/>
+      <c r="K50" s="10" t="str">
         <f aca="false">IF(J50="","",J50+14)</f>
         <v/>
       </c>
-      <c r="L50" s="4"/>
-      <c r="M50" s="4"/>
+      <c r="L50" s="11"/>
+      <c r="M50" s="8"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="n">
+      <c r="A51" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C51" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D51" s="5" t="s">
+      <c r="D51" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E51" s="6"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="6"/>
-      <c r="K51" s="6" t="str">
+      <c r="E51" s="10"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="11"/>
+      <c r="J51" s="12"/>
+      <c r="K51" s="10" t="str">
         <f aca="false">IF(J51="","",J51+14)</f>
         <v/>
       </c>
-      <c r="L51" s="4"/>
-      <c r="M51" s="4"/>
+      <c r="L51" s="11"/>
+      <c r="M51" s="8"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="n">
+      <c r="A52" s="8" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="D52" s="5" t="s">
+      <c r="D52" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E52" s="6"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
-      <c r="J52" s="6"/>
-      <c r="K52" s="6" t="str">
+      <c r="E52" s="10"/>
+      <c r="F52" s="11"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="11"/>
+      <c r="J52" s="12"/>
+      <c r="K52" s="10" t="str">
         <f aca="false">IF(J52="","",J52+14)</f>
         <v/>
       </c>
-      <c r="L52" s="4"/>
-      <c r="M52" s="4"/>
+      <c r="L52" s="11"/>
+      <c r="M52" s="8"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="n">
+      <c r="A53" s="8" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C53" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="D53" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E53" s="6"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="6"/>
-      <c r="K53" s="6" t="str">
+      <c r="D53" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E53" s="10"/>
+      <c r="F53" s="11"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="12"/>
+      <c r="K53" s="10" t="str">
         <f aca="false">IF(J53="","",J53+14)</f>
         <v/>
       </c>
-      <c r="L53" s="4"/>
-      <c r="M53" s="4"/>
+      <c r="L53" s="11"/>
+      <c r="M53" s="8"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="n">
+      <c r="A54" s="8" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D54" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E54" s="6"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
-      <c r="J54" s="6"/>
-      <c r="K54" s="6" t="str">
+      <c r="D54" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E54" s="10"/>
+      <c r="F54" s="11"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="8"/>
+      <c r="I54" s="11"/>
+      <c r="J54" s="12"/>
+      <c r="K54" s="10" t="str">
         <f aca="false">IF(J54="","",J54+14)</f>
         <v/>
       </c>
-      <c r="L54" s="4"/>
-      <c r="M54" s="4"/>
+      <c r="L54" s="11"/>
+      <c r="M54" s="8"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="n">
+      <c r="A55" s="8" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="C55" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D55" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E55" s="6"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="4"/>
-      <c r="H55" s="4"/>
-      <c r="I55" s="4"/>
-      <c r="J55" s="6"/>
-      <c r="K55" s="6" t="str">
+      <c r="D55" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E55" s="10"/>
+      <c r="F55" s="11"/>
+      <c r="G55" s="8"/>
+      <c r="H55" s="8"/>
+      <c r="I55" s="11"/>
+      <c r="J55" s="12"/>
+      <c r="K55" s="10" t="str">
         <f aca="false">IF(J55="","",J55+14)</f>
         <v/>
       </c>
-      <c r="L55" s="4"/>
-      <c r="M55" s="4"/>
+      <c r="L55" s="11"/>
+      <c r="M55" s="8"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="n">
+      <c r="A56" s="8" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C56" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="D56" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E56" s="6"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4"/>
-      <c r="J56" s="6"/>
-      <c r="K56" s="6" t="str">
+      <c r="D56" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E56" s="10"/>
+      <c r="F56" s="11"/>
+      <c r="G56" s="8"/>
+      <c r="H56" s="8"/>
+      <c r="I56" s="11"/>
+      <c r="J56" s="12"/>
+      <c r="K56" s="10" t="str">
         <f aca="false">IF(J56="","",J56+14)</f>
         <v/>
       </c>
-      <c r="L56" s="4"/>
-      <c r="M56" s="4"/>
+      <c r="L56" s="11"/>
+      <c r="M56" s="8"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="n">
+      <c r="A57" s="8" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="C57" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D57" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E57" s="6"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="4"/>
-      <c r="J57" s="6"/>
-      <c r="K57" s="6" t="str">
+      <c r="D57" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E57" s="10"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="8"/>
+      <c r="H57" s="8"/>
+      <c r="I57" s="11"/>
+      <c r="J57" s="12"/>
+      <c r="K57" s="10" t="str">
         <f aca="false">IF(J57="","",J57+14)</f>
         <v/>
       </c>
-      <c r="L57" s="4"/>
-      <c r="M57" s="4"/>
+      <c r="L57" s="11"/>
+      <c r="M57" s="8"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="4" t="n">
+      <c r="A58" s="8" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C58" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D58" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E58" s="6" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F58" s="4" t="s">
+      <c r="D58" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F58" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="4" t="s">
+      <c r="G58" s="8"/>
+      <c r="H58" s="8"/>
+      <c r="I58" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="J58" s="6" t="n">
-        <v>46302</v>
-      </c>
-      <c r="K58" s="6" t="n">
+      <c r="J58" s="12" t="n">
+        <v>46213</v>
+      </c>
+      <c r="K58" s="10" t="n">
         <f aca="false">IF(J58="","",J58+14)</f>
-        <v>46316</v>
-      </c>
-      <c r="L58" s="4"/>
-      <c r="M58" s="4"/>
+        <v>46227</v>
+      </c>
+      <c r="L58" s="11"/>
+      <c r="M58" s="8"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="4" t="n">
+      <c r="A59" s="8" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="C59" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="D59" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E59" s="6"/>
-      <c r="F59" s="4"/>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
-      <c r="I59" s="4"/>
-      <c r="J59" s="6"/>
-      <c r="K59" s="6" t="str">
+      <c r="D59" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>46214</v>
+      </c>
+      <c r="F59" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="G59" s="8"/>
+      <c r="H59" s="8"/>
+      <c r="I59" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="J59" s="12" t="n">
+        <v>46214</v>
+      </c>
+      <c r="K59" s="10" t="n">
         <f aca="false">IF(J59="","",J59+14)</f>
-        <v/>
-      </c>
-      <c r="L59" s="4"/>
-      <c r="M59" s="4"/>
+        <v>46228</v>
+      </c>
+      <c r="L59" s="11"/>
+      <c r="M59" s="8"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4" t="n">
+      <c r="A60" s="8" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C60" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="D60" s="8" t="s">
+      <c r="D60" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E60" s="6"/>
-      <c r="F60" s="4"/>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4"/>
-      <c r="I60" s="4"/>
-      <c r="J60" s="6"/>
-      <c r="K60" s="6" t="str">
+      <c r="E60" s="10" t="n">
+        <v>46217</v>
+      </c>
+      <c r="F60" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="G60" s="8"/>
+      <c r="H60" s="8"/>
+      <c r="I60" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="J60" s="15" t="n">
+        <v>46217</v>
+      </c>
+      <c r="K60" s="10" t="n">
         <f aca="false">IF(J60="","",J60+14)</f>
-        <v/>
-      </c>
-      <c r="L60" s="4"/>
-      <c r="M60" s="4"/>
+        <v>46231</v>
+      </c>
+      <c r="L60" s="11"/>
+      <c r="M60" s="8"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4" t="n">
+      <c r="A61" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="C61" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D61" s="8" t="s">
+      <c r="D61" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E61" s="6"/>
-      <c r="F61" s="4"/>
-      <c r="G61" s="4"/>
-      <c r="H61" s="4"/>
-      <c r="I61" s="4"/>
-      <c r="J61" s="6"/>
-      <c r="K61" s="6" t="str">
+      <c r="E61" s="10"/>
+      <c r="F61" s="11"/>
+      <c r="G61" s="8"/>
+      <c r="H61" s="8"/>
+      <c r="I61" s="11"/>
+      <c r="J61" s="12"/>
+      <c r="K61" s="10" t="str">
         <f aca="false">IF(J61="","",J61+14)</f>
         <v/>
       </c>
-      <c r="L61" s="4"/>
-      <c r="M61" s="4"/>
+      <c r="L61" s="11"/>
+      <c r="M61" s="8"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="4" t="n">
+      <c r="A62" s="8" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="C62" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="D62" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E62" s="6"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4"/>
-      <c r="I62" s="4"/>
-      <c r="J62" s="6"/>
-      <c r="K62" s="6" t="str">
+      <c r="D62" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E62" s="10"/>
+      <c r="F62" s="11"/>
+      <c r="G62" s="8"/>
+      <c r="H62" s="8"/>
+      <c r="I62" s="11"/>
+      <c r="J62" s="12"/>
+      <c r="K62" s="10" t="str">
         <f aca="false">IF(J62="","",J62+14)</f>
         <v/>
       </c>
-      <c r="L62" s="4"/>
-      <c r="M62" s="4"/>
+      <c r="L62" s="11"/>
+      <c r="M62" s="8"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="4" t="n">
+      <c r="A63" s="8" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="C63" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="D63" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E63" s="6"/>
-      <c r="F63" s="4"/>
-      <c r="G63" s="4"/>
-      <c r="H63" s="4"/>
-      <c r="I63" s="4"/>
-      <c r="J63" s="6"/>
-      <c r="K63" s="6" t="str">
+      <c r="D63" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E63" s="10"/>
+      <c r="F63" s="11"/>
+      <c r="G63" s="8"/>
+      <c r="H63" s="8"/>
+      <c r="I63" s="11"/>
+      <c r="J63" s="12"/>
+      <c r="K63" s="10" t="str">
         <f aca="false">IF(J63="","",J63+14)</f>
         <v/>
       </c>
-      <c r="L63" s="4"/>
-      <c r="M63" s="4"/>
+      <c r="L63" s="11"/>
+      <c r="M63" s="8"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="4" t="n">
+      <c r="A64" s="8" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B64" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="C64" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D64" s="8" t="s">
+      <c r="D64" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E64" s="6"/>
-      <c r="F64" s="4"/>
-      <c r="G64" s="4"/>
-      <c r="H64" s="4"/>
-      <c r="I64" s="4"/>
-      <c r="J64" s="6"/>
-      <c r="K64" s="6" t="str">
+      <c r="E64" s="10"/>
+      <c r="F64" s="11"/>
+      <c r="G64" s="8"/>
+      <c r="H64" s="8"/>
+      <c r="I64" s="11"/>
+      <c r="J64" s="12"/>
+      <c r="K64" s="10" t="str">
         <f aca="false">IF(J64="","",J64+14)</f>
         <v/>
       </c>
-      <c r="L64" s="4"/>
-      <c r="M64" s="4"/>
+      <c r="L64" s="11"/>
+      <c r="M64" s="8"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="n">
+      <c r="A65" s="8" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B65" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="C65" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="D65" s="5" t="s">
+      <c r="D65" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E65" s="6"/>
-      <c r="F65" s="4"/>
-      <c r="G65" s="4"/>
-      <c r="H65" s="4"/>
-      <c r="I65" s="4"/>
-      <c r="J65" s="6"/>
-      <c r="K65" s="6" t="str">
+      <c r="E65" s="10"/>
+      <c r="F65" s="11"/>
+      <c r="G65" s="8"/>
+      <c r="H65" s="8"/>
+      <c r="I65" s="11"/>
+      <c r="J65" s="12"/>
+      <c r="K65" s="10" t="str">
         <f aca="false">IF(J65="","",J65+14)</f>
         <v/>
       </c>
-      <c r="L65" s="4"/>
-      <c r="M65" s="4"/>
+      <c r="L65" s="11"/>
+      <c r="M65" s="8"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="n">
+      <c r="A66" s="8" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B66" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="C66" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D66" s="5" t="s">
+      <c r="D66" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E66" s="6"/>
-      <c r="F66" s="4"/>
-      <c r="G66" s="4"/>
-      <c r="H66" s="4"/>
-      <c r="I66" s="4"/>
-      <c r="J66" s="6"/>
-      <c r="K66" s="6" t="str">
+      <c r="E66" s="10"/>
+      <c r="F66" s="11"/>
+      <c r="G66" s="8"/>
+      <c r="H66" s="8"/>
+      <c r="I66" s="11"/>
+      <c r="J66" s="12"/>
+      <c r="K66" s="10" t="str">
         <f aca="false">IF(J66="","",J66+14)</f>
         <v/>
       </c>
-      <c r="L66" s="4"/>
-      <c r="M66" s="4"/>
+      <c r="L66" s="11"/>
+      <c r="M66" s="8"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="4" t="n">
+      <c r="A67" s="8" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B67" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="C67" s="4" t="s">
+      <c r="C67" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D67" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E67" s="6"/>
-      <c r="F67" s="4"/>
-      <c r="G67" s="4"/>
-      <c r="H67" s="4"/>
-      <c r="I67" s="4"/>
-      <c r="J67" s="6"/>
-      <c r="K67" s="6" t="str">
+      <c r="D67" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E67" s="10"/>
+      <c r="F67" s="11"/>
+      <c r="G67" s="8"/>
+      <c r="H67" s="8"/>
+      <c r="I67" s="11"/>
+      <c r="J67" s="12"/>
+      <c r="K67" s="10" t="str">
         <f aca="false">IF(J67="","",J67+14)</f>
         <v/>
       </c>
-      <c r="L67" s="4"/>
-      <c r="M67" s="4"/>
+      <c r="L67" s="11"/>
+      <c r="M67" s="8"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="4" t="n">
+      <c r="A68" s="8" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="C68" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="D68" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E68" s="6"/>
-      <c r="F68" s="4"/>
-      <c r="G68" s="4"/>
-      <c r="H68" s="4"/>
-      <c r="I68" s="4"/>
-      <c r="J68" s="6"/>
-      <c r="K68" s="6" t="str">
+      <c r="D68" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E68" s="10"/>
+      <c r="F68" s="11"/>
+      <c r="G68" s="8"/>
+      <c r="H68" s="8"/>
+      <c r="I68" s="11"/>
+      <c r="J68" s="12"/>
+      <c r="K68" s="10" t="str">
         <f aca="false">IF(J68="","",J68+14)</f>
         <v/>
       </c>
-      <c r="L68" s="4"/>
-      <c r="M68" s="4"/>
+      <c r="L68" s="11"/>
+      <c r="M68" s="8"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="4" t="n">
+      <c r="A69" s="8" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B69" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="C69" s="4" t="s">
+      <c r="C69" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D69" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E69" s="6"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
-      <c r="H69" s="4"/>
-      <c r="I69" s="4"/>
-      <c r="J69" s="6"/>
-      <c r="K69" s="6" t="str">
+      <c r="D69" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E69" s="10"/>
+      <c r="F69" s="11"/>
+      <c r="G69" s="8"/>
+      <c r="H69" s="8"/>
+      <c r="I69" s="11"/>
+      <c r="J69" s="12"/>
+      <c r="K69" s="10" t="str">
         <f aca="false">IF(J69="","",J69+14)</f>
         <v/>
       </c>
-      <c r="L69" s="4"/>
-      <c r="M69" s="4"/>
+      <c r="L69" s="11"/>
+      <c r="M69" s="8"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="4" t="n">
+      <c r="A70" s="8" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="B70" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="C70" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D70" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E70" s="6"/>
-      <c r="F70" s="4"/>
-      <c r="G70" s="4"/>
-      <c r="H70" s="4"/>
-      <c r="I70" s="4"/>
-      <c r="J70" s="6"/>
-      <c r="K70" s="6" t="str">
+      <c r="D70" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E70" s="10"/>
+      <c r="F70" s="11"/>
+      <c r="G70" s="8"/>
+      <c r="H70" s="8"/>
+      <c r="I70" s="11"/>
+      <c r="J70" s="12"/>
+      <c r="K70" s="10" t="str">
         <f aca="false">IF(J70="","",J70+14)</f>
         <v/>
       </c>
-      <c r="L70" s="4"/>
-      <c r="M70" s="4"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="8"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="4" t="n">
+      <c r="A71" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="B71" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="C71" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="D71" s="8" t="s">
+      <c r="D71" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E71" s="6"/>
-      <c r="F71" s="4"/>
-      <c r="G71" s="4"/>
-      <c r="H71" s="4"/>
-      <c r="I71" s="4"/>
-      <c r="J71" s="6"/>
-      <c r="K71" s="6" t="str">
+      <c r="E71" s="10"/>
+      <c r="F71" s="11"/>
+      <c r="G71" s="8"/>
+      <c r="H71" s="8"/>
+      <c r="I71" s="11"/>
+      <c r="J71" s="12"/>
+      <c r="K71" s="10" t="str">
         <f aca="false">IF(J71="","",J71+14)</f>
         <v/>
       </c>
-      <c r="L71" s="4"/>
-      <c r="M71" s="4"/>
+      <c r="L71" s="11"/>
+      <c r="M71" s="8"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="4" t="n">
+      <c r="A72" s="8" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="4" t="s">
+      <c r="B72" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C72" s="4" t="s">
+      <c r="C72" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="D72" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E72" s="6"/>
-      <c r="F72" s="4"/>
-      <c r="G72" s="4"/>
-      <c r="H72" s="4"/>
-      <c r="I72" s="4"/>
-      <c r="J72" s="6"/>
-      <c r="K72" s="6" t="str">
+      <c r="D72" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E72" s="10"/>
+      <c r="F72" s="11"/>
+      <c r="G72" s="8"/>
+      <c r="H72" s="8"/>
+      <c r="I72" s="11"/>
+      <c r="J72" s="12"/>
+      <c r="K72" s="10" t="str">
         <f aca="false">IF(J72="","",J72+14)</f>
         <v/>
       </c>
-      <c r="L72" s="4"/>
-      <c r="M72" s="4"/>
+      <c r="L72" s="11"/>
+      <c r="M72" s="8"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="4" t="n">
+      <c r="A73" s="8" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="4" t="s">
+      <c r="B73" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C73" s="4" t="s">
+      <c r="C73" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="D73" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E73" s="6"/>
-      <c r="F73" s="4"/>
-      <c r="G73" s="4"/>
-      <c r="H73" s="4"/>
-      <c r="I73" s="4"/>
-      <c r="J73" s="6"/>
-      <c r="K73" s="6" t="str">
+      <c r="D73" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E73" s="10"/>
+      <c r="F73" s="11"/>
+      <c r="G73" s="8"/>
+      <c r="H73" s="8"/>
+      <c r="I73" s="11"/>
+      <c r="J73" s="12"/>
+      <c r="K73" s="10" t="str">
         <f aca="false">IF(J73="","",J73+14)</f>
         <v/>
       </c>
-      <c r="L73" s="4"/>
-      <c r="M73" s="4"/>
+      <c r="L73" s="11"/>
+      <c r="M73" s="8"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4" t="n">
+      <c r="A74" s="8" t="n">
         <v>73</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C74" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="D74" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E74" s="6"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
-      <c r="I74" s="4"/>
-      <c r="J74" s="6"/>
-      <c r="K74" s="6" t="str">
+      <c r="D74" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E74" s="10"/>
+      <c r="F74" s="11"/>
+      <c r="G74" s="8"/>
+      <c r="H74" s="8"/>
+      <c r="I74" s="11"/>
+      <c r="J74" s="12"/>
+      <c r="K74" s="10" t="str">
         <f aca="false">IF(J74="","",J74+14)</f>
         <v/>
       </c>
-      <c r="L74" s="4"/>
-      <c r="M74" s="4"/>
+      <c r="L74" s="11"/>
+      <c r="M74" s="8"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="4" t="n">
+      <c r="A75" s="8" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="B75" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C75" s="4" t="s">
+      <c r="C75" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D75" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E75" s="6"/>
-      <c r="F75" s="4"/>
-      <c r="G75" s="4"/>
-      <c r="H75" s="4"/>
-      <c r="I75" s="4"/>
-      <c r="J75" s="6"/>
-      <c r="K75" s="6" t="str">
+      <c r="D75" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E75" s="10"/>
+      <c r="F75" s="11"/>
+      <c r="G75" s="8"/>
+      <c r="H75" s="8"/>
+      <c r="I75" s="11"/>
+      <c r="J75" s="12"/>
+      <c r="K75" s="10" t="str">
         <f aca="false">IF(J75="","",J75+14)</f>
         <v/>
       </c>
-      <c r="L75" s="4"/>
-      <c r="M75" s="4"/>
+      <c r="L75" s="11"/>
+      <c r="M75" s="8"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="4" t="n">
+      <c r="A76" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B76" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="C76" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="D76" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E76" s="6"/>
-      <c r="F76" s="4"/>
-      <c r="G76" s="4"/>
-      <c r="H76" s="4"/>
-      <c r="I76" s="4"/>
-      <c r="J76" s="6"/>
-      <c r="K76" s="6" t="str">
+      <c r="D76" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E76" s="10"/>
+      <c r="F76" s="11"/>
+      <c r="G76" s="8"/>
+      <c r="H76" s="8"/>
+      <c r="I76" s="11"/>
+      <c r="J76" s="12"/>
+      <c r="K76" s="10" t="str">
         <f aca="false">IF(J76="","",J76+14)</f>
         <v/>
       </c>
-      <c r="L76" s="4"/>
-      <c r="M76" s="4"/>
+      <c r="L76" s="11"/>
+      <c r="M76" s="8"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="4" t="n">
+      <c r="A77" s="8" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="4" t="s">
+      <c r="B77" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C77" s="4" t="s">
+      <c r="C77" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="D77" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E77" s="6"/>
-      <c r="F77" s="4"/>
-      <c r="G77" s="4"/>
-      <c r="H77" s="4"/>
-      <c r="I77" s="4"/>
-      <c r="J77" s="6"/>
-      <c r="K77" s="6" t="str">
+      <c r="D77" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E77" s="10"/>
+      <c r="F77" s="11"/>
+      <c r="G77" s="8"/>
+      <c r="H77" s="8"/>
+      <c r="I77" s="11"/>
+      <c r="J77" s="12"/>
+      <c r="K77" s="10" t="str">
         <f aca="false">IF(J77="","",J77+14)</f>
         <v/>
       </c>
-      <c r="L77" s="4"/>
-      <c r="M77" s="4"/>
+      <c r="L77" s="11"/>
+      <c r="M77" s="8"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="4" t="n">
+      <c r="A78" s="8" t="n">
         <v>77</v>
       </c>
-      <c r="B78" s="4" t="s">
+      <c r="B78" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C78" s="4" t="s">
+      <c r="C78" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D78" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E78" s="6"/>
-      <c r="F78" s="4"/>
-      <c r="G78" s="4"/>
-      <c r="H78" s="4"/>
-      <c r="I78" s="4"/>
-      <c r="J78" s="6"/>
-      <c r="K78" s="6" t="str">
+      <c r="D78" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E78" s="10"/>
+      <c r="F78" s="11"/>
+      <c r="G78" s="8"/>
+      <c r="H78" s="8"/>
+      <c r="I78" s="11"/>
+      <c r="J78" s="12"/>
+      <c r="K78" s="10" t="str">
         <f aca="false">IF(J78="","",J78+14)</f>
         <v/>
       </c>
-      <c r="L78" s="4"/>
-      <c r="M78" s="4"/>
+      <c r="L78" s="11"/>
+      <c r="M78" s="8"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="4" t="n">
+      <c r="A79" s="8" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="4" t="s">
+      <c r="B79" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C79" s="4" t="s">
+      <c r="C79" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="D79" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E79" s="6"/>
-      <c r="F79" s="4"/>
-      <c r="G79" s="4"/>
-      <c r="H79" s="4"/>
-      <c r="I79" s="4"/>
-      <c r="J79" s="6"/>
-      <c r="K79" s="6" t="str">
+      <c r="D79" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E79" s="10"/>
+      <c r="F79" s="11"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="8"/>
+      <c r="I79" s="11"/>
+      <c r="J79" s="12"/>
+      <c r="K79" s="10" t="str">
         <f aca="false">IF(J79="","",J79+14)</f>
         <v/>
       </c>
-      <c r="L79" s="4"/>
-      <c r="M79" s="4"/>
+      <c r="L79" s="11"/>
+      <c r="M79" s="8"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="4" t="n">
+      <c r="A80" s="8" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="4" t="s">
+      <c r="B80" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C80" s="4" t="s">
+      <c r="C80" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="D80" s="8" t="s">
+      <c r="D80" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E80" s="6"/>
-      <c r="F80" s="4"/>
-      <c r="G80" s="4"/>
-      <c r="H80" s="4"/>
-      <c r="I80" s="4"/>
-      <c r="J80" s="6"/>
-      <c r="K80" s="6" t="str">
+      <c r="E80" s="10"/>
+      <c r="F80" s="11"/>
+      <c r="G80" s="8"/>
+      <c r="H80" s="8"/>
+      <c r="I80" s="11"/>
+      <c r="J80" s="12"/>
+      <c r="K80" s="10" t="str">
         <f aca="false">IF(J80="","",J80+14)</f>
         <v/>
       </c>
-      <c r="L80" s="4"/>
-      <c r="M80" s="4"/>
+      <c r="L80" s="11"/>
+      <c r="M80" s="8"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="4" t="n">
+      <c r="A81" s="8" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="4" t="s">
+      <c r="B81" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="C81" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D81" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E81" s="6"/>
-      <c r="F81" s="4"/>
-      <c r="G81" s="4"/>
-      <c r="H81" s="4"/>
-      <c r="I81" s="4"/>
-      <c r="J81" s="6"/>
-      <c r="K81" s="6" t="str">
+      <c r="D81" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E81" s="10"/>
+      <c r="F81" s="11"/>
+      <c r="G81" s="8"/>
+      <c r="H81" s="8"/>
+      <c r="I81" s="11"/>
+      <c r="J81" s="12"/>
+      <c r="K81" s="10" t="str">
         <f aca="false">IF(J81="","",J81+14)</f>
         <v/>
       </c>
-      <c r="L81" s="4"/>
-      <c r="M81" s="4"/>
+      <c r="L81" s="11"/>
+      <c r="M81" s="8"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="4" t="n">
+      <c r="A82" s="8" t="n">
         <v>81</v>
       </c>
-      <c r="B82" s="4" t="s">
+      <c r="B82" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C82" s="4" t="s">
+      <c r="C82" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="D82" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E82" s="6"/>
-      <c r="F82" s="4"/>
-      <c r="G82" s="4"/>
-      <c r="H82" s="4"/>
-      <c r="I82" s="4"/>
-      <c r="J82" s="6"/>
-      <c r="K82" s="6" t="str">
+      <c r="D82" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E82" s="10"/>
+      <c r="F82" s="11"/>
+      <c r="G82" s="8"/>
+      <c r="H82" s="8"/>
+      <c r="I82" s="11"/>
+      <c r="J82" s="12"/>
+      <c r="K82" s="10" t="str">
         <f aca="false">IF(J82="","",J82+14)</f>
         <v/>
       </c>
-      <c r="L82" s="4"/>
-      <c r="M82" s="4"/>
+      <c r="L82" s="11"/>
+      <c r="M82" s="8"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="4" t="n">
+      <c r="A83" s="8" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="4" t="s">
+      <c r="B83" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C83" s="4" t="s">
+      <c r="C83" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="D83" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E83" s="6"/>
-      <c r="F83" s="4"/>
-      <c r="G83" s="4"/>
-      <c r="H83" s="4"/>
-      <c r="I83" s="4"/>
-      <c r="J83" s="6"/>
-      <c r="K83" s="6" t="str">
+      <c r="D83" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E83" s="10"/>
+      <c r="F83" s="11"/>
+      <c r="G83" s="8"/>
+      <c r="H83" s="8"/>
+      <c r="I83" s="11"/>
+      <c r="J83" s="12"/>
+      <c r="K83" s="10" t="str">
         <f aca="false">IF(J83="","",J83+14)</f>
         <v/>
       </c>
-      <c r="L83" s="4"/>
-      <c r="M83" s="4"/>
+      <c r="L83" s="11"/>
+      <c r="M83" s="8"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="4" t="n">
+      <c r="A84" s="8" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="4" t="s">
+      <c r="B84" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C84" s="4" t="s">
+      <c r="C84" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="D84" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E84" s="6"/>
-      <c r="F84" s="4"/>
-      <c r="G84" s="4"/>
-      <c r="H84" s="4"/>
-      <c r="I84" s="4"/>
-      <c r="J84" s="6"/>
-      <c r="K84" s="6" t="str">
+      <c r="D84" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E84" s="10"/>
+      <c r="F84" s="11"/>
+      <c r="G84" s="8"/>
+      <c r="H84" s="8"/>
+      <c r="I84" s="11"/>
+      <c r="J84" s="12"/>
+      <c r="K84" s="10" t="str">
         <f aca="false">IF(J84="","",J84+14)</f>
         <v/>
       </c>
-      <c r="L84" s="4"/>
-      <c r="M84" s="4"/>
+      <c r="L84" s="11"/>
+      <c r="M84" s="8"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="4" t="n">
+      <c r="A85" s="8" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="B85" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C85" s="4" t="s">
+      <c r="C85" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="D85" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E85" s="6"/>
-      <c r="F85" s="4"/>
-      <c r="G85" s="4"/>
-      <c r="H85" s="4"/>
-      <c r="I85" s="4"/>
-      <c r="J85" s="6"/>
-      <c r="K85" s="6" t="str">
+      <c r="D85" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E85" s="10"/>
+      <c r="F85" s="11"/>
+      <c r="G85" s="8"/>
+      <c r="H85" s="8"/>
+      <c r="I85" s="11"/>
+      <c r="J85" s="12"/>
+      <c r="K85" s="10" t="str">
         <f aca="false">IF(J85="","",J85+14)</f>
         <v/>
       </c>
-      <c r="L85" s="4"/>
-      <c r="M85" s="4"/>
+      <c r="L85" s="11"/>
+      <c r="M85" s="8"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="4" t="n">
+      <c r="A86" s="8" t="n">
         <v>85</v>
       </c>
-      <c r="B86" s="4" t="s">
+      <c r="B86" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C86" s="4" t="s">
+      <c r="C86" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="D86" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E86" s="6"/>
-      <c r="F86" s="4"/>
-      <c r="G86" s="4"/>
-      <c r="H86" s="4"/>
-      <c r="I86" s="4"/>
-      <c r="J86" s="6"/>
-      <c r="K86" s="6" t="str">
+      <c r="D86" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E86" s="10"/>
+      <c r="F86" s="11"/>
+      <c r="G86" s="8"/>
+      <c r="H86" s="8"/>
+      <c r="I86" s="11"/>
+      <c r="J86" s="12"/>
+      <c r="K86" s="10" t="str">
         <f aca="false">IF(J86="","",J86+14)</f>
         <v/>
       </c>
-      <c r="L86" s="4"/>
-      <c r="M86" s="4"/>
+      <c r="L86" s="11"/>
+      <c r="M86" s="8"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="4" t="n">
+      <c r="A87" s="8" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="4" t="s">
+      <c r="B87" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C87" s="4" t="s">
+      <c r="C87" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="D87" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E87" s="6"/>
-      <c r="F87" s="4"/>
-      <c r="G87" s="4"/>
-      <c r="H87" s="4"/>
-      <c r="I87" s="4"/>
-      <c r="J87" s="6"/>
-      <c r="K87" s="6" t="str">
+      <c r="D87" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E87" s="10"/>
+      <c r="F87" s="11"/>
+      <c r="G87" s="8"/>
+      <c r="H87" s="8"/>
+      <c r="I87" s="11"/>
+      <c r="J87" s="12"/>
+      <c r="K87" s="10" t="str">
         <f aca="false">IF(J87="","",J87+14)</f>
         <v/>
       </c>
-      <c r="L87" s="4"/>
-      <c r="M87" s="4"/>
+      <c r="L87" s="11"/>
+      <c r="M87" s="8"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="4" t="n">
+      <c r="A88" s="8" t="n">
         <v>87</v>
       </c>
-      <c r="B88" s="4" t="s">
+      <c r="B88" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C88" s="4" t="s">
+      <c r="C88" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="D88" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E88" s="6"/>
-      <c r="F88" s="4"/>
-      <c r="G88" s="4"/>
-      <c r="H88" s="4"/>
-      <c r="I88" s="4"/>
-      <c r="J88" s="6"/>
-      <c r="K88" s="6" t="str">
+      <c r="D88" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E88" s="10"/>
+      <c r="F88" s="11"/>
+      <c r="G88" s="8"/>
+      <c r="H88" s="8"/>
+      <c r="I88" s="11"/>
+      <c r="J88" s="12"/>
+      <c r="K88" s="10" t="str">
         <f aca="false">IF(J88="","",J88+14)</f>
         <v/>
       </c>
-      <c r="L88" s="4"/>
-      <c r="M88" s="4"/>
+      <c r="L88" s="11"/>
+      <c r="M88" s="8"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="4" t="n">
+      <c r="A89" s="8" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="4" t="s">
+      <c r="B89" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C89" s="4" t="s">
+      <c r="C89" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="D89" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E89" s="6"/>
-      <c r="F89" s="4"/>
-      <c r="G89" s="4"/>
-      <c r="H89" s="4"/>
-      <c r="I89" s="4"/>
-      <c r="J89" s="6"/>
-      <c r="K89" s="6" t="str">
+      <c r="D89" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E89" s="10"/>
+      <c r="F89" s="11"/>
+      <c r="G89" s="8"/>
+      <c r="H89" s="8"/>
+      <c r="I89" s="11"/>
+      <c r="J89" s="12"/>
+      <c r="K89" s="10" t="str">
         <f aca="false">IF(J89="","",J89+14)</f>
         <v/>
       </c>
-      <c r="L89" s="4"/>
-      <c r="M89" s="4"/>
+      <c r="L89" s="11"/>
+      <c r="M89" s="8"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="4" t="n">
+      <c r="A90" s="8" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="4" t="s">
+      <c r="B90" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C90" s="4" t="s">
+      <c r="C90" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="D90" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E90" s="6"/>
-      <c r="F90" s="4"/>
-      <c r="G90" s="4"/>
-      <c r="H90" s="4"/>
-      <c r="I90" s="4"/>
-      <c r="J90" s="6"/>
-      <c r="K90" s="6" t="str">
+      <c r="D90" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E90" s="10"/>
+      <c r="F90" s="11"/>
+      <c r="G90" s="8"/>
+      <c r="H90" s="8"/>
+      <c r="I90" s="11"/>
+      <c r="J90" s="12"/>
+      <c r="K90" s="10" t="str">
         <f aca="false">IF(J90="","",J90+14)</f>
         <v/>
       </c>
-      <c r="L90" s="4"/>
-      <c r="M90" s="4"/>
+      <c r="L90" s="11"/>
+      <c r="M90" s="8"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="4" t="n">
+      <c r="A91" s="8" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="4" t="s">
+      <c r="B91" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C91" s="4" t="s">
+      <c r="C91" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="D91" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E91" s="6"/>
-      <c r="F91" s="4"/>
-      <c r="G91" s="4"/>
-      <c r="H91" s="4"/>
-      <c r="I91" s="4"/>
-      <c r="J91" s="6"/>
-      <c r="K91" s="6" t="str">
+      <c r="D91" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E91" s="10"/>
+      <c r="F91" s="11"/>
+      <c r="G91" s="8"/>
+      <c r="H91" s="8"/>
+      <c r="I91" s="11"/>
+      <c r="J91" s="12"/>
+      <c r="K91" s="10" t="str">
         <f aca="false">IF(J91="","",J91+14)</f>
         <v/>
       </c>
-      <c r="L91" s="4"/>
-      <c r="M91" s="4"/>
+      <c r="L91" s="11"/>
+      <c r="M91" s="8"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="4" t="n">
+      <c r="A92" s="8" t="n">
         <v>91</v>
       </c>
-      <c r="B92" s="4" t="s">
+      <c r="B92" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C92" s="4" t="s">
+      <c r="C92" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="D92" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E92" s="6"/>
-      <c r="F92" s="4"/>
-      <c r="G92" s="4"/>
-      <c r="H92" s="4"/>
-      <c r="I92" s="4"/>
-      <c r="J92" s="6"/>
-      <c r="K92" s="6" t="str">
+      <c r="D92" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E92" s="10"/>
+      <c r="F92" s="11"/>
+      <c r="G92" s="8"/>
+      <c r="H92" s="8"/>
+      <c r="I92" s="11"/>
+      <c r="J92" s="12"/>
+      <c r="K92" s="10" t="str">
         <f aca="false">IF(J92="","",J92+14)</f>
         <v/>
       </c>
-      <c r="L92" s="4"/>
-      <c r="M92" s="4"/>
+      <c r="L92" s="11"/>
+      <c r="M92" s="8"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="4" t="n">
+      <c r="A93" s="8" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="4" t="s">
+      <c r="B93" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C93" s="4" t="s">
+      <c r="C93" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="D93" s="8" t="s">
+      <c r="D93" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E93" s="6"/>
-      <c r="F93" s="4"/>
-      <c r="G93" s="4"/>
-      <c r="H93" s="4"/>
-      <c r="I93" s="4"/>
-      <c r="J93" s="6"/>
-      <c r="K93" s="6" t="str">
+      <c r="E93" s="10"/>
+      <c r="F93" s="11"/>
+      <c r="G93" s="8"/>
+      <c r="H93" s="8"/>
+      <c r="I93" s="11"/>
+      <c r="J93" s="12"/>
+      <c r="K93" s="10" t="str">
         <f aca="false">IF(J93="","",J93+14)</f>
         <v/>
       </c>
-      <c r="L93" s="4"/>
-      <c r="M93" s="4"/>
+      <c r="L93" s="11"/>
+      <c r="M93" s="8"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="4" t="n">
+      <c r="A94" s="8" t="n">
         <v>93</v>
       </c>
-      <c r="B94" s="4" t="s">
+      <c r="B94" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="C94" s="4" t="s">
+      <c r="C94" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="D94" s="8" t="s">
+      <c r="D94" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E94" s="6"/>
-      <c r="F94" s="4"/>
-      <c r="G94" s="4"/>
-      <c r="H94" s="4"/>
-      <c r="I94" s="4"/>
-      <c r="J94" s="6"/>
-      <c r="K94" s="6" t="str">
+      <c r="E94" s="10"/>
+      <c r="F94" s="11"/>
+      <c r="G94" s="8"/>
+      <c r="H94" s="8"/>
+      <c r="I94" s="11"/>
+      <c r="J94" s="12"/>
+      <c r="K94" s="10" t="str">
         <f aca="false">IF(J94="","",J94+14)</f>
         <v/>
       </c>
-      <c r="L94" s="4"/>
-      <c r="M94" s="4"/>
+      <c r="L94" s="11"/>
+      <c r="M94" s="8"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="4" t="n">
+      <c r="A95" s="8" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="4" t="s">
+      <c r="B95" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="C95" s="4" t="s">
+      <c r="C95" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="D95" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E95" s="6"/>
-      <c r="F95" s="4"/>
-      <c r="G95" s="4"/>
-      <c r="H95" s="4"/>
-      <c r="I95" s="4"/>
-      <c r="J95" s="6"/>
-      <c r="K95" s="6" t="str">
+      <c r="D95" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E95" s="10"/>
+      <c r="F95" s="11"/>
+      <c r="G95" s="8"/>
+      <c r="H95" s="8"/>
+      <c r="I95" s="11"/>
+      <c r="J95" s="12"/>
+      <c r="K95" s="10" t="str">
         <f aca="false">IF(J95="","",J95+14)</f>
         <v/>
       </c>
-      <c r="L95" s="4"/>
-      <c r="M95" s="4"/>
+      <c r="L95" s="11"/>
+      <c r="M95" s="8"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="4" t="n">
+      <c r="A96" s="8" t="n">
         <v>95</v>
       </c>
-      <c r="B96" s="4" t="s">
+      <c r="B96" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="C96" s="4" t="s">
+      <c r="C96" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="D96" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E96" s="6"/>
-      <c r="F96" s="4"/>
-      <c r="G96" s="4"/>
-      <c r="H96" s="4"/>
-      <c r="I96" s="4"/>
-      <c r="J96" s="6"/>
-      <c r="K96" s="6" t="str">
+      <c r="D96" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E96" s="10"/>
+      <c r="F96" s="11"/>
+      <c r="G96" s="8"/>
+      <c r="H96" s="8"/>
+      <c r="I96" s="11"/>
+      <c r="J96" s="12"/>
+      <c r="K96" s="10" t="str">
         <f aca="false">IF(J96="","",J96+14)</f>
         <v/>
       </c>
-      <c r="L96" s="4"/>
-      <c r="M96" s="4"/>
+      <c r="L96" s="11"/>
+      <c r="M96" s="8"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="4" t="n">
+      <c r="A97" s="8" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="4" t="s">
+      <c r="B97" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="C97" s="4" t="s">
+      <c r="C97" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="D97" s="8" t="s">
+      <c r="D97" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E97" s="6"/>
-      <c r="F97" s="4"/>
-      <c r="G97" s="4"/>
-      <c r="H97" s="4"/>
-      <c r="I97" s="4"/>
-      <c r="J97" s="6"/>
-      <c r="K97" s="6" t="str">
+      <c r="E97" s="10"/>
+      <c r="F97" s="11"/>
+      <c r="G97" s="8"/>
+      <c r="H97" s="8"/>
+      <c r="I97" s="11"/>
+      <c r="J97" s="12"/>
+      <c r="K97" s="10" t="str">
         <f aca="false">IF(J97="","",J97+14)</f>
         <v/>
       </c>
-      <c r="L97" s="4"/>
-      <c r="M97" s="4"/>
+      <c r="L97" s="11"/>
+      <c r="M97" s="8"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="4" t="n">
+      <c r="A98" s="8" t="n">
         <v>97</v>
       </c>
-      <c r="B98" s="4" t="s">
+      <c r="B98" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="C98" s="4" t="s">
+      <c r="C98" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="D98" s="8" t="s">
+      <c r="D98" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E98" s="6"/>
-      <c r="F98" s="4"/>
-      <c r="G98" s="4"/>
-      <c r="H98" s="4"/>
-      <c r="I98" s="4"/>
-      <c r="J98" s="6"/>
-      <c r="K98" s="6" t="str">
+      <c r="E98" s="10"/>
+      <c r="F98" s="11"/>
+      <c r="G98" s="8"/>
+      <c r="H98" s="8"/>
+      <c r="I98" s="11"/>
+      <c r="J98" s="12"/>
+      <c r="K98" s="10" t="str">
         <f aca="false">IF(J98="","",J98+14)</f>
         <v/>
       </c>
-      <c r="L98" s="4"/>
-      <c r="M98" s="4"/>
+      <c r="L98" s="11"/>
+      <c r="M98" s="8"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="4" t="n">
+      <c r="A99" s="8" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="4" t="s">
+      <c r="B99" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="C99" s="4" t="s">
+      <c r="C99" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="D99" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E99" s="6"/>
-      <c r="F99" s="4"/>
-      <c r="G99" s="4"/>
-      <c r="H99" s="4"/>
-      <c r="I99" s="4"/>
-      <c r="J99" s="6"/>
-      <c r="K99" s="6" t="str">
+      <c r="D99" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E99" s="10"/>
+      <c r="F99" s="11"/>
+      <c r="G99" s="8"/>
+      <c r="H99" s="8"/>
+      <c r="I99" s="11"/>
+      <c r="J99" s="12"/>
+      <c r="K99" s="10" t="str">
         <f aca="false">IF(J99="","",J99+14)</f>
         <v/>
       </c>
-      <c r="L99" s="4"/>
-      <c r="M99" s="4"/>
+      <c r="L99" s="11"/>
+      <c r="M99" s="8"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="4" t="n">
+      <c r="A100" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="B100" s="4" t="s">
+      <c r="B100" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C100" s="4" t="s">
+      <c r="C100" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="D100" s="5" t="s">
+      <c r="D100" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E100" s="6"/>
-      <c r="F100" s="4"/>
-      <c r="G100" s="4"/>
-      <c r="H100" s="4"/>
-      <c r="I100" s="4"/>
-      <c r="J100" s="6"/>
-      <c r="K100" s="6" t="str">
+      <c r="E100" s="10"/>
+      <c r="F100" s="11"/>
+      <c r="G100" s="8"/>
+      <c r="H100" s="8"/>
+      <c r="I100" s="11"/>
+      <c r="J100" s="12"/>
+      <c r="K100" s="10" t="str">
         <f aca="false">IF(J100="","",J100+14)</f>
         <v/>
       </c>
-      <c r="L100" s="4"/>
-      <c r="M100" s="4"/>
+      <c r="L100" s="11"/>
+      <c r="M100" s="8"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="4" t="n">
+      <c r="A101" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="B101" s="4" t="s">
+      <c r="B101" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C101" s="4" t="s">
+      <c r="C101" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="D101" s="5" t="s">
+      <c r="D101" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E101" s="6"/>
-      <c r="F101" s="4"/>
-      <c r="G101" s="4"/>
-      <c r="H101" s="4"/>
-      <c r="I101" s="4"/>
-      <c r="J101" s="6"/>
-      <c r="K101" s="6" t="str">
+      <c r="E101" s="10"/>
+      <c r="F101" s="11"/>
+      <c r="G101" s="8"/>
+      <c r="H101" s="8"/>
+      <c r="I101" s="11"/>
+      <c r="J101" s="12"/>
+      <c r="K101" s="10" t="str">
         <f aca="false">IF(J101="","",J101+14)</f>
         <v/>
       </c>
-      <c r="L101" s="4"/>
-      <c r="M101" s="4"/>
+      <c r="L101" s="11"/>
+      <c r="M101" s="8"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="4" t="n">
+      <c r="A102" s="8" t="n">
         <v>101</v>
       </c>
-      <c r="B102" s="4" t="s">
+      <c r="B102" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C102" s="4" t="s">
+      <c r="C102" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="D102" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E102" s="6"/>
-      <c r="F102" s="4"/>
-      <c r="G102" s="4"/>
-      <c r="H102" s="4"/>
-      <c r="I102" s="4"/>
-      <c r="J102" s="6"/>
-      <c r="K102" s="6" t="str">
+      <c r="D102" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E102" s="10"/>
+      <c r="F102" s="11"/>
+      <c r="G102" s="8"/>
+      <c r="H102" s="8"/>
+      <c r="I102" s="11"/>
+      <c r="J102" s="12"/>
+      <c r="K102" s="10" t="str">
         <f aca="false">IF(J102="","",J102+14)</f>
         <v/>
       </c>
-      <c r="L102" s="4"/>
-      <c r="M102" s="4"/>
+      <c r="L102" s="11"/>
+      <c r="M102" s="8"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="4" t="n">
+      <c r="A103" s="8" t="n">
         <v>102</v>
       </c>
-      <c r="B103" s="4" t="s">
+      <c r="B103" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C103" s="4" t="s">
+      <c r="C103" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="D103" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E103" s="6"/>
-      <c r="F103" s="4"/>
-      <c r="G103" s="4"/>
-      <c r="H103" s="4"/>
-      <c r="I103" s="4"/>
-      <c r="J103" s="6"/>
-      <c r="K103" s="6" t="str">
+      <c r="D103" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E103" s="10"/>
+      <c r="F103" s="11"/>
+      <c r="G103" s="8"/>
+      <c r="H103" s="8"/>
+      <c r="I103" s="11"/>
+      <c r="J103" s="12"/>
+      <c r="K103" s="10" t="str">
         <f aca="false">IF(J103="","",J103+14)</f>
         <v/>
       </c>
-      <c r="L103" s="4"/>
-      <c r="M103" s="4"/>
+      <c r="L103" s="11"/>
+      <c r="M103" s="8"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="4" t="n">
+      <c r="A104" s="8" t="n">
         <v>103</v>
       </c>
-      <c r="B104" s="4" t="s">
+      <c r="B104" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C104" s="4" t="s">
+      <c r="C104" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="D104" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E104" s="6"/>
-      <c r="F104" s="4"/>
-      <c r="G104" s="4"/>
-      <c r="H104" s="4"/>
-      <c r="I104" s="4"/>
-      <c r="J104" s="6"/>
-      <c r="K104" s="6" t="str">
+      <c r="D104" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E104" s="10"/>
+      <c r="F104" s="11"/>
+      <c r="G104" s="8"/>
+      <c r="H104" s="8"/>
+      <c r="I104" s="11"/>
+      <c r="J104" s="12"/>
+      <c r="K104" s="10" t="str">
         <f aca="false">IF(J104="","",J104+14)</f>
         <v/>
       </c>
-      <c r="L104" s="4"/>
-      <c r="M104" s="4"/>
+      <c r="L104" s="11"/>
+      <c r="M104" s="8"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="4" t="n">
+      <c r="A105" s="8" t="n">
         <v>104</v>
       </c>
-      <c r="B105" s="4" t="s">
+      <c r="B105" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C105" s="4" t="s">
+      <c r="C105" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D105" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E105" s="6"/>
-      <c r="F105" s="4"/>
-      <c r="G105" s="4"/>
-      <c r="H105" s="4"/>
-      <c r="I105" s="4"/>
-      <c r="J105" s="6"/>
-      <c r="K105" s="6" t="str">
+      <c r="D105" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E105" s="10"/>
+      <c r="F105" s="11"/>
+      <c r="G105" s="8"/>
+      <c r="H105" s="8"/>
+      <c r="I105" s="11"/>
+      <c r="J105" s="12"/>
+      <c r="K105" s="10" t="str">
         <f aca="false">IF(J105="","",J105+14)</f>
         <v/>
       </c>
-      <c r="L105" s="4"/>
-      <c r="M105" s="4"/>
+      <c r="L105" s="11"/>
+      <c r="M105" s="8"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="4" t="n">
+      <c r="A106" s="8" t="n">
         <v>105</v>
       </c>
-      <c r="B106" s="4" t="s">
+      <c r="B106" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C106" s="4" t="s">
+      <c r="C106" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="D106" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E106" s="6"/>
-      <c r="F106" s="4"/>
-      <c r="G106" s="4"/>
-      <c r="H106" s="4"/>
-      <c r="I106" s="4"/>
-      <c r="J106" s="6"/>
-      <c r="K106" s="6" t="str">
+      <c r="D106" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E106" s="10"/>
+      <c r="F106" s="11"/>
+      <c r="G106" s="8"/>
+      <c r="H106" s="8"/>
+      <c r="I106" s="11"/>
+      <c r="J106" s="12"/>
+      <c r="K106" s="10" t="str">
         <f aca="false">IF(J106="","",J106+14)</f>
         <v/>
       </c>
-      <c r="L106" s="4"/>
-      <c r="M106" s="4"/>
+      <c r="L106" s="11"/>
+      <c r="M106" s="8"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="4" t="n">
+      <c r="A107" s="8" t="n">
         <v>106</v>
       </c>
-      <c r="B107" s="4" t="s">
+      <c r="B107" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C107" s="4" t="s">
+      <c r="C107" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="D107" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E107" s="6"/>
-      <c r="F107" s="4"/>
-      <c r="G107" s="4"/>
-      <c r="H107" s="4"/>
-      <c r="I107" s="4"/>
-      <c r="J107" s="6"/>
-      <c r="K107" s="6" t="str">
+      <c r="D107" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E107" s="10"/>
+      <c r="F107" s="11"/>
+      <c r="G107" s="8"/>
+      <c r="H107" s="8"/>
+      <c r="I107" s="11"/>
+      <c r="J107" s="12"/>
+      <c r="K107" s="10" t="str">
         <f aca="false">IF(J107="","",J107+14)</f>
         <v/>
       </c>
-      <c r="L107" s="4"/>
-      <c r="M107" s="4"/>
+      <c r="L107" s="11"/>
+      <c r="M107" s="8"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="4" t="n">
+      <c r="A108" s="8" t="n">
         <v>107</v>
       </c>
-      <c r="B108" s="4" t="s">
+      <c r="B108" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C108" s="4" t="s">
+      <c r="C108" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="D108" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E108" s="6"/>
-      <c r="F108" s="4"/>
-      <c r="G108" s="4"/>
-      <c r="H108" s="4"/>
-      <c r="I108" s="4"/>
-      <c r="J108" s="6"/>
-      <c r="K108" s="6" t="str">
+      <c r="D108" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E108" s="10"/>
+      <c r="F108" s="11"/>
+      <c r="G108" s="8"/>
+      <c r="H108" s="8"/>
+      <c r="I108" s="11"/>
+      <c r="J108" s="12"/>
+      <c r="K108" s="10" t="str">
         <f aca="false">IF(J108="","",J108+14)</f>
         <v/>
       </c>
-      <c r="L108" s="4"/>
-      <c r="M108" s="4"/>
+      <c r="L108" s="11"/>
+      <c r="M108" s="8"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="4" t="n">
+      <c r="A109" s="8" t="n">
         <v>108</v>
       </c>
-      <c r="B109" s="4" t="s">
+      <c r="B109" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C109" s="4" t="s">
+      <c r="C109" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="D109" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E109" s="6"/>
-      <c r="F109" s="4"/>
-      <c r="G109" s="4"/>
-      <c r="H109" s="4"/>
-      <c r="I109" s="4"/>
-      <c r="J109" s="6"/>
-      <c r="K109" s="6" t="str">
+      <c r="D109" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E109" s="10"/>
+      <c r="F109" s="11"/>
+      <c r="G109" s="8"/>
+      <c r="H109" s="8"/>
+      <c r="I109" s="11"/>
+      <c r="J109" s="12"/>
+      <c r="K109" s="10" t="str">
         <f aca="false">IF(J109="","",J109+14)</f>
         <v/>
       </c>
-      <c r="L109" s="4"/>
-      <c r="M109" s="4"/>
+      <c r="L109" s="11"/>
+      <c r="M109" s="8"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="4" t="n">
+      <c r="A110" s="8" t="n">
         <v>109</v>
       </c>
-      <c r="B110" s="4" t="s">
+      <c r="B110" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C110" s="4" t="s">
+      <c r="C110" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="D110" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E110" s="6"/>
-      <c r="F110" s="4"/>
-      <c r="G110" s="4"/>
-      <c r="H110" s="4"/>
-      <c r="I110" s="4"/>
-      <c r="J110" s="6"/>
-      <c r="K110" s="6" t="str">
+      <c r="D110" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E110" s="10"/>
+      <c r="F110" s="11"/>
+      <c r="G110" s="8"/>
+      <c r="H110" s="8"/>
+      <c r="I110" s="11"/>
+      <c r="J110" s="12"/>
+      <c r="K110" s="10" t="str">
         <f aca="false">IF(J110="","",J110+14)</f>
         <v/>
       </c>
-      <c r="L110" s="4"/>
-      <c r="M110" s="4"/>
+      <c r="L110" s="11"/>
+      <c r="M110" s="8"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="4" t="n">
+      <c r="A111" s="8" t="n">
         <v>110</v>
       </c>
-      <c r="B111" s="4" t="s">
+      <c r="B111" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C111" s="4" t="s">
+      <c r="C111" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="D111" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E111" s="6"/>
-      <c r="F111" s="4"/>
-      <c r="G111" s="4"/>
-      <c r="H111" s="4"/>
-      <c r="I111" s="4"/>
-      <c r="J111" s="6"/>
-      <c r="K111" s="6" t="str">
+      <c r="D111" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E111" s="10"/>
+      <c r="F111" s="11"/>
+      <c r="G111" s="8"/>
+      <c r="H111" s="8"/>
+      <c r="I111" s="11"/>
+      <c r="J111" s="12"/>
+      <c r="K111" s="10" t="str">
         <f aca="false">IF(J111="","",J111+14)</f>
         <v/>
       </c>
-      <c r="L111" s="4"/>
-      <c r="M111" s="4"/>
+      <c r="L111" s="11"/>
+      <c r="M111" s="8"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="4" t="n">
+      <c r="A112" s="8" t="n">
         <v>111</v>
       </c>
-      <c r="B112" s="4" t="s">
+      <c r="B112" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="C112" s="4" t="s">
+      <c r="C112" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="D112" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E112" s="6"/>
-      <c r="F112" s="4"/>
-      <c r="G112" s="4"/>
-      <c r="H112" s="4"/>
-      <c r="I112" s="4"/>
-      <c r="J112" s="6"/>
-      <c r="K112" s="6" t="str">
+      <c r="D112" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E112" s="10"/>
+      <c r="F112" s="11"/>
+      <c r="G112" s="8"/>
+      <c r="H112" s="8"/>
+      <c r="I112" s="11"/>
+      <c r="J112" s="12"/>
+      <c r="K112" s="10" t="str">
         <f aca="false">IF(J112="","",J112+14)</f>
         <v/>
       </c>
-      <c r="L112" s="4"/>
-      <c r="M112" s="4"/>
+      <c r="L112" s="11"/>
+      <c r="M112" s="8"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="4" t="n">
+      <c r="A113" s="8" t="n">
         <v>112</v>
       </c>
-      <c r="B113" s="4" t="s">
+      <c r="B113" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="C113" s="4" t="s">
+      <c r="C113" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="D113" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E113" s="6"/>
-      <c r="F113" s="4"/>
-      <c r="G113" s="4"/>
-      <c r="H113" s="4"/>
-      <c r="I113" s="4"/>
-      <c r="J113" s="6"/>
-      <c r="K113" s="6" t="str">
+      <c r="D113" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E113" s="10"/>
+      <c r="F113" s="11"/>
+      <c r="G113" s="8"/>
+      <c r="H113" s="8"/>
+      <c r="I113" s="11"/>
+      <c r="J113" s="12"/>
+      <c r="K113" s="10" t="str">
         <f aca="false">IF(J113="","",J113+14)</f>
         <v/>
       </c>
-      <c r="L113" s="4"/>
-      <c r="M113" s="4"/>
+      <c r="L113" s="11"/>
+      <c r="M113" s="8"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="4" t="n">
+      <c r="A114" s="8" t="n">
         <v>113</v>
       </c>
-      <c r="B114" s="4" t="s">
+      <c r="B114" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="C114" s="4" t="s">
+      <c r="C114" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="D114" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E114" s="6"/>
-      <c r="F114" s="4"/>
-      <c r="G114" s="4"/>
-      <c r="H114" s="4"/>
-      <c r="I114" s="4"/>
-      <c r="J114" s="6"/>
-      <c r="K114" s="6" t="str">
+      <c r="D114" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E114" s="10"/>
+      <c r="F114" s="11"/>
+      <c r="G114" s="8"/>
+      <c r="H114" s="8"/>
+      <c r="I114" s="11"/>
+      <c r="J114" s="12"/>
+      <c r="K114" s="10" t="str">
         <f aca="false">IF(J114="","",J114+14)</f>
         <v/>
       </c>
-      <c r="L114" s="4"/>
-      <c r="M114" s="4"/>
+      <c r="L114" s="11"/>
+      <c r="M114" s="8"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="4" t="n">
+      <c r="A115" s="8" t="n">
         <v>114</v>
       </c>
-      <c r="B115" s="4" t="s">
+      <c r="B115" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="C115" s="4" t="s">
+      <c r="C115" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="D115" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E115" s="6"/>
-      <c r="F115" s="4"/>
-      <c r="G115" s="4"/>
-      <c r="H115" s="4"/>
-      <c r="I115" s="4"/>
-      <c r="J115" s="6"/>
-      <c r="K115" s="6" t="str">
+      <c r="D115" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E115" s="10"/>
+      <c r="F115" s="11"/>
+      <c r="G115" s="8"/>
+      <c r="H115" s="8"/>
+      <c r="I115" s="11"/>
+      <c r="J115" s="12"/>
+      <c r="K115" s="10" t="str">
         <f aca="false">IF(J115="","",J115+14)</f>
         <v/>
       </c>
-      <c r="L115" s="4"/>
-      <c r="M115" s="4"/>
+      <c r="L115" s="11"/>
+      <c r="M115" s="8"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="4" t="n">
+      <c r="A116" s="8" t="n">
         <v>115</v>
       </c>
-      <c r="B116" s="4" t="s">
+      <c r="B116" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="C116" s="4" t="s">
+      <c r="C116" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="D116" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E116" s="6"/>
-      <c r="F116" s="4"/>
-      <c r="G116" s="4"/>
-      <c r="H116" s="4"/>
-      <c r="I116" s="4"/>
-      <c r="J116" s="6"/>
-      <c r="K116" s="6" t="str">
+      <c r="D116" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E116" s="10"/>
+      <c r="F116" s="11"/>
+      <c r="G116" s="8"/>
+      <c r="H116" s="8"/>
+      <c r="I116" s="11"/>
+      <c r="J116" s="12"/>
+      <c r="K116" s="10" t="str">
         <f aca="false">IF(J116="","",J116+14)</f>
         <v/>
       </c>
-      <c r="L116" s="4"/>
-      <c r="M116" s="4"/>
+      <c r="L116" s="11"/>
+      <c r="M116" s="8"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="4" t="n">
+      <c r="A117" s="8" t="n">
         <v>116</v>
       </c>
-      <c r="B117" s="4" t="s">
+      <c r="B117" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="C117" s="4" t="s">
+      <c r="C117" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="D117" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E117" s="6"/>
-      <c r="F117" s="4"/>
-      <c r="G117" s="4"/>
-      <c r="H117" s="4"/>
-      <c r="I117" s="4"/>
-      <c r="J117" s="6"/>
-      <c r="K117" s="6" t="str">
+      <c r="D117" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E117" s="10"/>
+      <c r="F117" s="11"/>
+      <c r="G117" s="8"/>
+      <c r="H117" s="8"/>
+      <c r="I117" s="11"/>
+      <c r="J117" s="12"/>
+      <c r="K117" s="10" t="str">
         <f aca="false">IF(J117="","",J117+14)</f>
         <v/>
       </c>
-      <c r="L117" s="4"/>
-      <c r="M117" s="4"/>
+      <c r="L117" s="11"/>
+      <c r="M117" s="8"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="4" t="n">
+      <c r="A118" s="8" t="n">
         <v>117</v>
       </c>
-      <c r="B118" s="4" t="s">
+      <c r="B118" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="C118" s="4" t="s">
+      <c r="C118" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="D118" s="8" t="s">
+      <c r="D118" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E118" s="6"/>
-      <c r="F118" s="4"/>
-      <c r="G118" s="4"/>
-      <c r="H118" s="4"/>
-      <c r="I118" s="4"/>
-      <c r="J118" s="6"/>
-      <c r="K118" s="6" t="str">
+      <c r="E118" s="10"/>
+      <c r="F118" s="11"/>
+      <c r="G118" s="8"/>
+      <c r="H118" s="8"/>
+      <c r="I118" s="11"/>
+      <c r="J118" s="12"/>
+      <c r="K118" s="10" t="str">
         <f aca="false">IF(J118="","",J118+14)</f>
         <v/>
       </c>
-      <c r="L118" s="4"/>
-      <c r="M118" s="4"/>
+      <c r="L118" s="11"/>
+      <c r="M118" s="8"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="4" t="n">
+      <c r="A119" s="8" t="n">
         <v>118</v>
       </c>
-      <c r="B119" s="4" t="s">
+      <c r="B119" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="C119" s="4" t="s">
+      <c r="C119" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="D119" s="8" t="s">
+      <c r="D119" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E119" s="6"/>
-      <c r="F119" s="4"/>
-      <c r="G119" s="4"/>
-      <c r="H119" s="4"/>
-      <c r="I119" s="4"/>
-      <c r="J119" s="6"/>
-      <c r="K119" s="6" t="str">
+      <c r="E119" s="10"/>
+      <c r="F119" s="11"/>
+      <c r="G119" s="8"/>
+      <c r="H119" s="8"/>
+      <c r="I119" s="11"/>
+      <c r="J119" s="12"/>
+      <c r="K119" s="10" t="str">
         <f aca="false">IF(J119="","",J119+14)</f>
         <v/>
       </c>
-      <c r="L119" s="4"/>
-      <c r="M119" s="4"/>
+      <c r="L119" s="11"/>
+      <c r="M119" s="8"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="4" t="n">
+      <c r="A120" s="8" t="n">
         <v>119</v>
       </c>
-      <c r="B120" s="4" t="s">
+      <c r="B120" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="C120" s="4" t="s">
+      <c r="C120" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="D120" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E120" s="6"/>
-      <c r="F120" s="4"/>
-      <c r="G120" s="4"/>
-      <c r="H120" s="4"/>
-      <c r="I120" s="4"/>
-      <c r="J120" s="6"/>
-      <c r="K120" s="6" t="str">
+      <c r="D120" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E120" s="10"/>
+      <c r="F120" s="11"/>
+      <c r="G120" s="8"/>
+      <c r="H120" s="8"/>
+      <c r="I120" s="11"/>
+      <c r="J120" s="12"/>
+      <c r="K120" s="10" t="str">
         <f aca="false">IF(J120="","",J120+14)</f>
         <v/>
       </c>
-      <c r="L120" s="4"/>
-      <c r="M120" s="4"/>
+      <c r="L120" s="11"/>
+      <c r="M120" s="8"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="4" t="n">
+      <c r="A121" s="8" t="n">
         <v>120</v>
       </c>
-      <c r="B121" s="4" t="s">
+      <c r="B121" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="C121" s="4" t="s">
+      <c r="C121" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="D121" s="8" t="s">
+      <c r="D121" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E121" s="6"/>
-      <c r="F121" s="4"/>
-      <c r="G121" s="4"/>
-      <c r="H121" s="4"/>
-      <c r="I121" s="4"/>
-      <c r="J121" s="6"/>
-      <c r="K121" s="6" t="str">
+      <c r="E121" s="10"/>
+      <c r="F121" s="11"/>
+      <c r="G121" s="8"/>
+      <c r="H121" s="8"/>
+      <c r="I121" s="11"/>
+      <c r="J121" s="12"/>
+      <c r="K121" s="10" t="str">
         <f aca="false">IF(J121="","",J121+14)</f>
         <v/>
       </c>
-      <c r="L121" s="4"/>
-      <c r="M121" s="4"/>
+      <c r="L121" s="11"/>
+      <c r="M121" s="8"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="4" t="n">
+      <c r="A122" s="8" t="n">
         <v>121</v>
       </c>
-      <c r="B122" s="4" t="s">
+      <c r="B122" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="C122" s="4" t="s">
+      <c r="C122" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="D122" s="8" t="s">
+      <c r="D122" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E122" s="6"/>
-      <c r="F122" s="4"/>
-      <c r="G122" s="4"/>
-      <c r="H122" s="4"/>
-      <c r="I122" s="4"/>
-      <c r="J122" s="6"/>
-      <c r="K122" s="6" t="str">
+      <c r="E122" s="10"/>
+      <c r="F122" s="11"/>
+      <c r="G122" s="8"/>
+      <c r="H122" s="8"/>
+      <c r="I122" s="11"/>
+      <c r="J122" s="12"/>
+      <c r="K122" s="10" t="str">
         <f aca="false">IF(J122="","",J122+14)</f>
         <v/>
       </c>
-      <c r="L122" s="4"/>
-      <c r="M122" s="4"/>
+      <c r="L122" s="11"/>
+      <c r="M122" s="8"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="4" t="n">
+      <c r="A123" s="8" t="n">
         <v>122</v>
       </c>
-      <c r="B123" s="4" t="s">
+      <c r="B123" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="C123" s="4" t="s">
+      <c r="C123" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="D123" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E123" s="6"/>
-      <c r="F123" s="4"/>
-      <c r="G123" s="4"/>
-      <c r="H123" s="4"/>
-      <c r="I123" s="4"/>
-      <c r="J123" s="6"/>
-      <c r="K123" s="6" t="str">
+      <c r="D123" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E123" s="10"/>
+      <c r="F123" s="11"/>
+      <c r="G123" s="8"/>
+      <c r="H123" s="8"/>
+      <c r="I123" s="11"/>
+      <c r="J123" s="12"/>
+      <c r="K123" s="10" t="str">
         <f aca="false">IF(J123="","",J123+14)</f>
         <v/>
       </c>
-      <c r="L123" s="4"/>
-      <c r="M123" s="4"/>
+      <c r="L123" s="11"/>
+      <c r="M123" s="8"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="4" t="n">
+      <c r="A124" s="8" t="n">
         <v>123</v>
       </c>
-      <c r="B124" s="4" t="s">
+      <c r="B124" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="C124" s="4" t="s">
+      <c r="C124" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="D124" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E124" s="6"/>
-      <c r="F124" s="4"/>
-      <c r="G124" s="4"/>
-      <c r="H124" s="4"/>
-      <c r="I124" s="4"/>
-      <c r="J124" s="6"/>
-      <c r="K124" s="6" t="str">
+      <c r="D124" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E124" s="10"/>
+      <c r="F124" s="11"/>
+      <c r="G124" s="8"/>
+      <c r="H124" s="8"/>
+      <c r="I124" s="11"/>
+      <c r="J124" s="12"/>
+      <c r="K124" s="10" t="str">
         <f aca="false">IF(J124="","",J124+14)</f>
         <v/>
       </c>
-      <c r="L124" s="4"/>
-      <c r="M124" s="4"/>
+      <c r="L124" s="11"/>
+      <c r="M124" s="8"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="4" t="n">
+      <c r="A125" s="8" t="n">
         <v>124</v>
       </c>
-      <c r="B125" s="4" t="s">
+      <c r="B125" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="C125" s="4" t="s">
+      <c r="C125" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D125" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E125" s="6"/>
-      <c r="F125" s="4"/>
-      <c r="G125" s="4"/>
-      <c r="H125" s="4"/>
-      <c r="I125" s="4"/>
-      <c r="J125" s="6"/>
-      <c r="K125" s="6" t="str">
+      <c r="D125" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E125" s="10"/>
+      <c r="F125" s="11"/>
+      <c r="G125" s="8"/>
+      <c r="H125" s="8"/>
+      <c r="I125" s="11"/>
+      <c r="J125" s="12"/>
+      <c r="K125" s="10" t="str">
         <f aca="false">IF(J125="","",J125+14)</f>
         <v/>
       </c>
-      <c r="L125" s="4"/>
-      <c r="M125" s="4"/>
+      <c r="L125" s="11"/>
+      <c r="M125" s="8"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="4" t="n">
+      <c r="A126" s="8" t="n">
         <v>125</v>
       </c>
-      <c r="B126" s="4" t="s">
+      <c r="B126" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="C126" s="4" t="s">
+      <c r="C126" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D126" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E126" s="6"/>
-      <c r="F126" s="4"/>
-      <c r="G126" s="4"/>
-      <c r="H126" s="4"/>
-      <c r="I126" s="4"/>
-      <c r="J126" s="6"/>
-      <c r="K126" s="6" t="str">
+      <c r="D126" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E126" s="10"/>
+      <c r="F126" s="11"/>
+      <c r="G126" s="8"/>
+      <c r="H126" s="8"/>
+      <c r="I126" s="11"/>
+      <c r="J126" s="12"/>
+      <c r="K126" s="10" t="str">
         <f aca="false">IF(J126="","",J126+14)</f>
         <v/>
       </c>
-      <c r="L126" s="4"/>
-      <c r="M126" s="4"/>
+      <c r="L126" s="11"/>
+      <c r="M126" s="8"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="4" t="n">
+      <c r="A127" s="8" t="n">
         <v>126</v>
       </c>
-      <c r="B127" s="4" t="s">
+      <c r="B127" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="C127" s="4" t="s">
+      <c r="C127" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="D127" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E127" s="6"/>
-      <c r="F127" s="4"/>
-      <c r="G127" s="4"/>
-      <c r="H127" s="4"/>
-      <c r="I127" s="4"/>
-      <c r="J127" s="6"/>
-      <c r="K127" s="6" t="str">
+      <c r="D127" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E127" s="10"/>
+      <c r="F127" s="11"/>
+      <c r="G127" s="8"/>
+      <c r="H127" s="8"/>
+      <c r="I127" s="11"/>
+      <c r="J127" s="12"/>
+      <c r="K127" s="10" t="str">
         <f aca="false">IF(J127="","",J127+14)</f>
         <v/>
       </c>
-      <c r="L127" s="4"/>
-      <c r="M127" s="4"/>
+      <c r="L127" s="11"/>
+      <c r="M127" s="8"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="4" t="n">
+      <c r="A128" s="8" t="n">
         <v>127</v>
       </c>
-      <c r="B128" s="4" t="s">
+      <c r="B128" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="C128" s="4" t="s">
+      <c r="C128" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="D128" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E128" s="6"/>
-      <c r="F128" s="4"/>
-      <c r="G128" s="4"/>
-      <c r="H128" s="4"/>
-      <c r="I128" s="4"/>
-      <c r="J128" s="6"/>
-      <c r="K128" s="6" t="str">
+      <c r="D128" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E128" s="10"/>
+      <c r="F128" s="11"/>
+      <c r="G128" s="8"/>
+      <c r="H128" s="8"/>
+      <c r="I128" s="11"/>
+      <c r="J128" s="12"/>
+      <c r="K128" s="10" t="str">
         <f aca="false">IF(J128="","",J128+14)</f>
         <v/>
       </c>
-      <c r="L128" s="4"/>
-      <c r="M128" s="4"/>
+      <c r="L128" s="11"/>
+      <c r="M128" s="8"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="4" t="n">
+      <c r="A129" s="8" t="n">
         <v>128</v>
       </c>
-      <c r="B129" s="4" t="s">
+      <c r="B129" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="C129" s="4" t="s">
+      <c r="C129" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="D129" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E129" s="6"/>
-      <c r="F129" s="4"/>
-      <c r="G129" s="4"/>
-      <c r="H129" s="4"/>
-      <c r="I129" s="4"/>
-      <c r="J129" s="6"/>
-      <c r="K129" s="6" t="str">
+      <c r="D129" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E129" s="10"/>
+      <c r="F129" s="11"/>
+      <c r="G129" s="8"/>
+      <c r="H129" s="8"/>
+      <c r="I129" s="11"/>
+      <c r="J129" s="12"/>
+      <c r="K129" s="10" t="str">
         <f aca="false">IF(J129="","",J129+14)</f>
         <v/>
       </c>
-      <c r="L129" s="4"/>
-      <c r="M129" s="4"/>
+      <c r="L129" s="11"/>
+      <c r="M129" s="8"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="4" t="n">
+      <c r="A130" s="8" t="n">
         <v>129</v>
       </c>
-      <c r="B130" s="4" t="s">
+      <c r="B130" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="C130" s="4" t="s">
+      <c r="C130" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="D130" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E130" s="6"/>
-      <c r="F130" s="4"/>
-      <c r="G130" s="4"/>
-      <c r="H130" s="4"/>
-      <c r="I130" s="4"/>
-      <c r="J130" s="6"/>
-      <c r="K130" s="6" t="str">
+      <c r="D130" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E130" s="10"/>
+      <c r="F130" s="11"/>
+      <c r="G130" s="8"/>
+      <c r="H130" s="8"/>
+      <c r="I130" s="11"/>
+      <c r="J130" s="12"/>
+      <c r="K130" s="10" t="str">
         <f aca="false">IF(J130="","",J130+14)</f>
         <v/>
       </c>
-      <c r="L130" s="4"/>
-      <c r="M130" s="4"/>
+      <c r="L130" s="11"/>
+      <c r="M130" s="8"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="4" t="n">
+      <c r="A131" s="8" t="n">
         <v>130</v>
       </c>
-      <c r="B131" s="4" t="s">
+      <c r="B131" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="C131" s="4" t="s">
+      <c r="C131" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="D131" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E131" s="6"/>
-      <c r="F131" s="4"/>
-      <c r="G131" s="4"/>
-      <c r="H131" s="4"/>
-      <c r="I131" s="4"/>
-      <c r="J131" s="6"/>
-      <c r="K131" s="6" t="str">
+      <c r="D131" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E131" s="10"/>
+      <c r="F131" s="11"/>
+      <c r="G131" s="8"/>
+      <c r="H131" s="8"/>
+      <c r="I131" s="11"/>
+      <c r="J131" s="12"/>
+      <c r="K131" s="10" t="str">
         <f aca="false">IF(J131="","",J131+14)</f>
         <v/>
       </c>
-      <c r="L131" s="4"/>
-      <c r="M131" s="4"/>
+      <c r="L131" s="11"/>
+      <c r="M131" s="8"/>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="4" t="n">
+      <c r="A132" s="8" t="n">
         <v>131</v>
       </c>
-      <c r="B132" s="4" t="s">
+      <c r="B132" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="C132" s="4" t="s">
+      <c r="C132" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="D132" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E132" s="6"/>
-      <c r="F132" s="4"/>
-      <c r="G132" s="4"/>
-      <c r="H132" s="4"/>
-      <c r="I132" s="4"/>
-      <c r="J132" s="6"/>
-      <c r="K132" s="6" t="str">
+      <c r="D132" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E132" s="10"/>
+      <c r="F132" s="11"/>
+      <c r="G132" s="8"/>
+      <c r="H132" s="8"/>
+      <c r="I132" s="11"/>
+      <c r="J132" s="12"/>
+      <c r="K132" s="10" t="str">
         <f aca="false">IF(J132="","",J132+14)</f>
         <v/>
       </c>
-      <c r="L132" s="4"/>
-      <c r="M132" s="4"/>
+      <c r="L132" s="11"/>
+      <c r="M132" s="8"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="4" t="n">
+      <c r="A133" s="8" t="n">
         <v>132</v>
       </c>
-      <c r="B133" s="4" t="s">
+      <c r="B133" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="C133" s="4" t="s">
+      <c r="C133" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="D133" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E133" s="6"/>
-      <c r="F133" s="4"/>
-      <c r="G133" s="4"/>
-      <c r="H133" s="4"/>
-      <c r="I133" s="4"/>
-      <c r="J133" s="6"/>
-      <c r="K133" s="6" t="str">
+      <c r="D133" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E133" s="10"/>
+      <c r="F133" s="11"/>
+      <c r="G133" s="8"/>
+      <c r="H133" s="8"/>
+      <c r="I133" s="11"/>
+      <c r="J133" s="12"/>
+      <c r="K133" s="10" t="str">
         <f aca="false">IF(J133="","",J133+14)</f>
         <v/>
       </c>
-      <c r="L133" s="4"/>
-      <c r="M133" s="4"/>
+      <c r="L133" s="11"/>
+      <c r="M133" s="8"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="4" t="n">
+      <c r="A134" s="8" t="n">
         <v>133</v>
       </c>
-      <c r="B134" s="4" t="s">
+      <c r="B134" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="C134" s="4" t="s">
+      <c r="C134" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="D134" s="5" t="s">
+      <c r="D134" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E134" s="6"/>
-      <c r="F134" s="4"/>
-      <c r="G134" s="4"/>
-      <c r="H134" s="4"/>
-      <c r="I134" s="4"/>
-      <c r="J134" s="6"/>
-      <c r="K134" s="6" t="str">
+      <c r="E134" s="10"/>
+      <c r="F134" s="11"/>
+      <c r="G134" s="8"/>
+      <c r="H134" s="8"/>
+      <c r="I134" s="11"/>
+      <c r="J134" s="12"/>
+      <c r="K134" s="10" t="str">
         <f aca="false">IF(J134="","",J134+14)</f>
         <v/>
       </c>
-      <c r="L134" s="4"/>
-      <c r="M134" s="4"/>
+      <c r="L134" s="11"/>
+      <c r="M134" s="8"/>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="4" t="n">
+      <c r="A135" s="8" t="n">
         <v>134</v>
       </c>
-      <c r="B135" s="4" t="s">
+      <c r="B135" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="C135" s="4" t="s">
+      <c r="C135" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="D135" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E135" s="6"/>
-      <c r="F135" s="4"/>
-      <c r="G135" s="4"/>
-      <c r="H135" s="4"/>
-      <c r="I135" s="4"/>
-      <c r="J135" s="6"/>
-      <c r="K135" s="6" t="str">
+      <c r="D135" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E135" s="10"/>
+      <c r="F135" s="11"/>
+      <c r="G135" s="8"/>
+      <c r="H135" s="8"/>
+      <c r="I135" s="11"/>
+      <c r="J135" s="12"/>
+      <c r="K135" s="10" t="str">
         <f aca="false">IF(J135="","",J135+14)</f>
         <v/>
       </c>
-      <c r="L135" s="4"/>
-      <c r="M135" s="4"/>
+      <c r="L135" s="11"/>
+      <c r="M135" s="8"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="4" t="n">
+      <c r="A136" s="8" t="n">
         <v>135</v>
       </c>
-      <c r="B136" s="4" t="s">
+      <c r="B136" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="C136" s="4" t="s">
+      <c r="C136" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="D136" s="8" t="s">
+      <c r="D136" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E136" s="6"/>
-      <c r="F136" s="4"/>
-      <c r="G136" s="4"/>
-      <c r="H136" s="4"/>
-      <c r="I136" s="4"/>
-      <c r="J136" s="6"/>
-      <c r="K136" s="6" t="str">
+      <c r="E136" s="10"/>
+      <c r="F136" s="11"/>
+      <c r="G136" s="8"/>
+      <c r="H136" s="8"/>
+      <c r="I136" s="11"/>
+      <c r="J136" s="12"/>
+      <c r="K136" s="10" t="str">
         <f aca="false">IF(J136="","",J136+14)</f>
         <v/>
       </c>
-      <c r="L136" s="4"/>
-      <c r="M136" s="4"/>
+      <c r="L136" s="11"/>
+      <c r="M136" s="8"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="4" t="n">
+      <c r="A137" s="8" t="n">
         <v>136</v>
       </c>
-      <c r="B137" s="4" t="s">
+      <c r="B137" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="C137" s="4" t="s">
+      <c r="C137" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="D137" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E137" s="6"/>
-      <c r="F137" s="4"/>
-      <c r="G137" s="4"/>
-      <c r="H137" s="4"/>
-      <c r="I137" s="4"/>
-      <c r="J137" s="6"/>
-      <c r="K137" s="6" t="str">
+      <c r="D137" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E137" s="10"/>
+      <c r="F137" s="11"/>
+      <c r="G137" s="8"/>
+      <c r="H137" s="8"/>
+      <c r="I137" s="11"/>
+      <c r="J137" s="12"/>
+      <c r="K137" s="10" t="str">
         <f aca="false">IF(J137="","",J137+14)</f>
         <v/>
       </c>
-      <c r="L137" s="4"/>
-      <c r="M137" s="4"/>
+      <c r="L137" s="11"/>
+      <c r="M137" s="8"/>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="4" t="n">
+      <c r="A138" s="8" t="n">
         <v>137</v>
       </c>
-      <c r="B138" s="4" t="s">
+      <c r="B138" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="C138" s="4" t="s">
+      <c r="C138" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="D138" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E138" s="6"/>
-      <c r="F138" s="4"/>
-      <c r="G138" s="4"/>
-      <c r="H138" s="4"/>
-      <c r="I138" s="4"/>
-      <c r="J138" s="6"/>
-      <c r="K138" s="6" t="str">
+      <c r="D138" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E138" s="10"/>
+      <c r="F138" s="11"/>
+      <c r="G138" s="8"/>
+      <c r="H138" s="8"/>
+      <c r="I138" s="11"/>
+      <c r="J138" s="12"/>
+      <c r="K138" s="10" t="str">
         <f aca="false">IF(J138="","",J138+14)</f>
         <v/>
       </c>
-      <c r="L138" s="4"/>
-      <c r="M138" s="4"/>
+      <c r="L138" s="11"/>
+      <c r="M138" s="8"/>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="4" t="n">
+      <c r="A139" s="8" t="n">
         <v>138</v>
       </c>
-      <c r="B139" s="4" t="s">
+      <c r="B139" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="C139" s="4" t="s">
+      <c r="C139" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="D139" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E139" s="6"/>
-      <c r="F139" s="4"/>
-      <c r="G139" s="4"/>
-      <c r="H139" s="4"/>
-      <c r="I139" s="4"/>
-      <c r="J139" s="6"/>
-      <c r="K139" s="6" t="str">
+      <c r="D139" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E139" s="10"/>
+      <c r="F139" s="11"/>
+      <c r="G139" s="8"/>
+      <c r="H139" s="8"/>
+      <c r="I139" s="11"/>
+      <c r="J139" s="12"/>
+      <c r="K139" s="10" t="str">
         <f aca="false">IF(J139="","",J139+14)</f>
         <v/>
       </c>
-      <c r="L139" s="4"/>
-      <c r="M139" s="4"/>
+      <c r="L139" s="11"/>
+      <c r="M139" s="8"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="4" t="n">
+      <c r="A140" s="8" t="n">
         <v>139</v>
       </c>
-      <c r="B140" s="4" t="s">
+      <c r="B140" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="C140" s="4" t="s">
+      <c r="C140" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D140" s="5" t="s">
+      <c r="D140" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E140" s="6"/>
-      <c r="F140" s="4"/>
-      <c r="G140" s="4"/>
-      <c r="H140" s="4"/>
-      <c r="I140" s="4"/>
-      <c r="J140" s="6"/>
-      <c r="K140" s="6" t="str">
+      <c r="E140" s="10"/>
+      <c r="F140" s="11"/>
+      <c r="G140" s="8"/>
+      <c r="H140" s="8"/>
+      <c r="I140" s="11"/>
+      <c r="J140" s="12"/>
+      <c r="K140" s="10" t="str">
         <f aca="false">IF(J140="","",J140+14)</f>
         <v/>
       </c>
-      <c r="L140" s="4"/>
-      <c r="M140" s="4"/>
+      <c r="L140" s="11"/>
+      <c r="M140" s="8"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="4" t="n">
+      <c r="A141" s="8" t="n">
         <v>140</v>
       </c>
-      <c r="B141" s="4" t="s">
+      <c r="B141" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="C141" s="4" t="s">
+      <c r="C141" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="D141" s="5" t="s">
+      <c r="D141" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E141" s="6"/>
-      <c r="F141" s="4"/>
-      <c r="G141" s="4"/>
-      <c r="H141" s="4"/>
-      <c r="I141" s="4"/>
-      <c r="J141" s="6"/>
-      <c r="K141" s="6" t="str">
+      <c r="E141" s="10"/>
+      <c r="F141" s="11"/>
+      <c r="G141" s="8"/>
+      <c r="H141" s="8"/>
+      <c r="I141" s="11"/>
+      <c r="J141" s="12"/>
+      <c r="K141" s="10" t="str">
         <f aca="false">IF(J141="","",J141+14)</f>
         <v/>
       </c>
-      <c r="L141" s="4"/>
-      <c r="M141" s="4"/>
+      <c r="L141" s="11"/>
+      <c r="M141" s="8"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="4" t="n">
+      <c r="A142" s="8" t="n">
         <v>141</v>
       </c>
-      <c r="B142" s="4" t="s">
+      <c r="B142" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="C142" s="4" t="s">
+      <c r="C142" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="D142" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E142" s="6"/>
-      <c r="F142" s="4"/>
-      <c r="G142" s="4"/>
-      <c r="H142" s="4"/>
-      <c r="I142" s="4"/>
-      <c r="J142" s="6"/>
-      <c r="K142" s="6" t="str">
+      <c r="D142" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E142" s="10"/>
+      <c r="F142" s="11"/>
+      <c r="G142" s="8"/>
+      <c r="H142" s="8"/>
+      <c r="I142" s="11"/>
+      <c r="J142" s="12"/>
+      <c r="K142" s="10" t="str">
         <f aca="false">IF(J142="","",J142+14)</f>
         <v/>
       </c>
-      <c r="L142" s="4"/>
-      <c r="M142" s="4"/>
+      <c r="L142" s="11"/>
+      <c r="M142" s="8"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="4" t="n">
+      <c r="A143" s="8" t="n">
         <v>142</v>
       </c>
-      <c r="B143" s="4" t="s">
+      <c r="B143" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="C143" s="4" t="s">
+      <c r="C143" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="D143" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E143" s="6"/>
-      <c r="F143" s="4"/>
-      <c r="G143" s="4"/>
-      <c r="H143" s="4"/>
-      <c r="I143" s="4"/>
-      <c r="J143" s="6"/>
-      <c r="K143" s="6" t="str">
+      <c r="D143" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E143" s="10"/>
+      <c r="F143" s="11"/>
+      <c r="G143" s="8"/>
+      <c r="H143" s="8"/>
+      <c r="I143" s="11"/>
+      <c r="J143" s="12"/>
+      <c r="K143" s="10" t="str">
         <f aca="false">IF(J143="","",J143+14)</f>
         <v/>
       </c>
-      <c r="L143" s="4"/>
-      <c r="M143" s="4"/>
+      <c r="L143" s="11"/>
+      <c r="M143" s="8"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="4" t="n">
+      <c r="A144" s="8" t="n">
         <v>143</v>
       </c>
-      <c r="B144" s="4" t="s">
+      <c r="B144" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="C144" s="4" t="s">
+      <c r="C144" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="D144" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E144" s="6"/>
-      <c r="F144" s="4"/>
-      <c r="G144" s="4"/>
-      <c r="H144" s="4"/>
-      <c r="I144" s="4"/>
-      <c r="J144" s="6"/>
-      <c r="K144" s="6" t="str">
+      <c r="D144" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E144" s="10"/>
+      <c r="F144" s="11"/>
+      <c r="G144" s="8"/>
+      <c r="H144" s="8"/>
+      <c r="I144" s="11"/>
+      <c r="J144" s="12"/>
+      <c r="K144" s="10" t="str">
         <f aca="false">IF(J144="","",J144+14)</f>
         <v/>
       </c>
-      <c r="L144" s="4"/>
-      <c r="M144" s="4"/>
+      <c r="L144" s="11"/>
+      <c r="M144" s="8"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="4" t="n">
+      <c r="A145" s="8" t="n">
         <v>144</v>
       </c>
-      <c r="B145" s="4" t="s">
+      <c r="B145" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="C145" s="4" t="s">
+      <c r="C145" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="D145" s="5" t="s">
+      <c r="D145" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E145" s="6"/>
-      <c r="F145" s="4"/>
-      <c r="G145" s="4"/>
-      <c r="H145" s="4"/>
-      <c r="I145" s="4"/>
-      <c r="J145" s="6"/>
-      <c r="K145" s="6" t="str">
+      <c r="E145" s="10"/>
+      <c r="F145" s="11"/>
+      <c r="G145" s="8"/>
+      <c r="H145" s="8"/>
+      <c r="I145" s="11"/>
+      <c r="J145" s="12"/>
+      <c r="K145" s="10" t="str">
         <f aca="false">IF(J145="","",J145+14)</f>
         <v/>
       </c>
-      <c r="L145" s="4"/>
-      <c r="M145" s="4"/>
+      <c r="L145" s="11"/>
+      <c r="M145" s="8"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="4" t="n">
+      <c r="A146" s="8" t="n">
         <v>145</v>
       </c>
-      <c r="B146" s="4" t="s">
+      <c r="B146" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="C146" s="4" t="s">
+      <c r="C146" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="D146" s="5" t="s">
+      <c r="D146" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E146" s="6"/>
-      <c r="F146" s="4"/>
-      <c r="G146" s="4"/>
-      <c r="H146" s="4"/>
-      <c r="I146" s="4"/>
-      <c r="J146" s="6"/>
-      <c r="K146" s="6" t="str">
+      <c r="E146" s="10"/>
+      <c r="F146" s="11"/>
+      <c r="G146" s="8"/>
+      <c r="H146" s="8"/>
+      <c r="I146" s="11"/>
+      <c r="J146" s="12"/>
+      <c r="K146" s="10" t="str">
         <f aca="false">IF(J146="","",J146+14)</f>
         <v/>
       </c>
-      <c r="L146" s="4"/>
-      <c r="M146" s="4"/>
+      <c r="L146" s="11"/>
+      <c r="M146" s="8"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="4" t="n">
+      <c r="A147" s="8" t="n">
         <v>146</v>
       </c>
-      <c r="B147" s="4" t="s">
+      <c r="B147" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="C147" s="4" t="s">
+      <c r="C147" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D147" s="5" t="s">
+      <c r="D147" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E147" s="6"/>
-      <c r="F147" s="4"/>
-      <c r="G147" s="4"/>
-      <c r="H147" s="4"/>
-      <c r="I147" s="4"/>
-      <c r="J147" s="6"/>
-      <c r="K147" s="6" t="str">
+      <c r="E147" s="10"/>
+      <c r="F147" s="11"/>
+      <c r="G147" s="8"/>
+      <c r="H147" s="8"/>
+      <c r="I147" s="11"/>
+      <c r="J147" s="12"/>
+      <c r="K147" s="10" t="str">
         <f aca="false">IF(J147="","",J147+14)</f>
         <v/>
       </c>
-      <c r="L147" s="4"/>
-      <c r="M147" s="4"/>
+      <c r="L147" s="11"/>
+      <c r="M147" s="8"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="4" t="n">
+      <c r="A148" s="8" t="n">
         <v>147</v>
       </c>
-      <c r="B148" s="4" t="s">
+      <c r="B148" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="C148" s="4" t="s">
+      <c r="C148" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="D148" s="5" t="s">
+      <c r="D148" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E148" s="6"/>
-      <c r="F148" s="4"/>
-      <c r="G148" s="4"/>
-      <c r="H148" s="4"/>
-      <c r="I148" s="4"/>
-      <c r="J148" s="6"/>
-      <c r="K148" s="6" t="str">
+      <c r="E148" s="10"/>
+      <c r="F148" s="11"/>
+      <c r="G148" s="8"/>
+      <c r="H148" s="8"/>
+      <c r="I148" s="11"/>
+      <c r="J148" s="12"/>
+      <c r="K148" s="10" t="str">
         <f aca="false">IF(J148="","",J148+14)</f>
         <v/>
       </c>
-      <c r="L148" s="4"/>
-      <c r="M148" s="4"/>
+      <c r="L148" s="11"/>
+      <c r="M148" s="8"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="4" t="n">
+      <c r="A149" s="8" t="n">
         <v>148</v>
       </c>
-      <c r="B149" s="4" t="s">
+      <c r="B149" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="C149" s="4" t="s">
+      <c r="C149" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="D149" s="5" t="s">
+      <c r="D149" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E149" s="6"/>
-      <c r="F149" s="4"/>
-      <c r="G149" s="4"/>
-      <c r="H149" s="4"/>
-      <c r="I149" s="4"/>
-      <c r="J149" s="6"/>
-      <c r="K149" s="6" t="str">
+      <c r="E149" s="10"/>
+      <c r="F149" s="11"/>
+      <c r="G149" s="8"/>
+      <c r="H149" s="8"/>
+      <c r="I149" s="11"/>
+      <c r="J149" s="12"/>
+      <c r="K149" s="10" t="str">
         <f aca="false">IF(J149="","",J149+14)</f>
         <v/>
       </c>
-      <c r="L149" s="4"/>
-      <c r="M149" s="4"/>
+      <c r="L149" s="11"/>
+      <c r="M149" s="8"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="4" t="n">
+      <c r="A150" s="8" t="n">
         <v>149</v>
       </c>
-      <c r="B150" s="4" t="s">
+      <c r="B150" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="C150" s="4" t="s">
+      <c r="C150" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="D150" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E150" s="6"/>
-      <c r="F150" s="4"/>
-      <c r="G150" s="4"/>
-      <c r="H150" s="4"/>
-      <c r="I150" s="4"/>
-      <c r="J150" s="6"/>
-      <c r="K150" s="6" t="str">
+      <c r="D150" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E150" s="10"/>
+      <c r="F150" s="11"/>
+      <c r="G150" s="8"/>
+      <c r="H150" s="8"/>
+      <c r="I150" s="11"/>
+      <c r="J150" s="12"/>
+      <c r="K150" s="10" t="str">
         <f aca="false">IF(J150="","",J150+14)</f>
         <v/>
       </c>
-      <c r="L150" s="4"/>
-      <c r="M150" s="4"/>
+      <c r="L150" s="11"/>
+      <c r="M150" s="8"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="4" t="n">
+      <c r="A151" s="8" t="n">
         <v>150</v>
       </c>
-      <c r="B151" s="4" t="s">
+      <c r="B151" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="C151" s="4" t="s">
+      <c r="C151" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="D151" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E151" s="6"/>
-      <c r="F151" s="4"/>
-      <c r="G151" s="4"/>
-      <c r="H151" s="4"/>
-      <c r="I151" s="4"/>
-      <c r="J151" s="6"/>
-      <c r="K151" s="6" t="str">
+      <c r="D151" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E151" s="10"/>
+      <c r="F151" s="11"/>
+      <c r="G151" s="8"/>
+      <c r="H151" s="8"/>
+      <c r="I151" s="11"/>
+      <c r="J151" s="12"/>
+      <c r="K151" s="10" t="str">
         <f aca="false">IF(J151="","",J151+14)</f>
         <v/>
       </c>
-      <c r="L151" s="4"/>
-      <c r="M151" s="4"/>
+      <c r="L151" s="11"/>
+      <c r="M151" s="8"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I151">
@@ -5158,147 +5209,147 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="16" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="B3" s="11" t="n">
+      <c r="B3" s="18" t="n">
         <f aca="false">COUNTA(Tracker!C2:C151)</f>
         <v>150</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="B4" s="11" t="n">
+      <c r="B4" s="18" t="n">
         <f aca="false">COUNTIF(Tracker!I2:I151,"Solved")</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B5" s="18" t="n">
         <f aca="false">COUNTIF(Tracker!I2:I151,"Solved with Help")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="18" t="n">
         <f aca="false">COUNTIF(Tracker!I2:I151,"Attempted")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="18" t="n">
         <f aca="false">COUNTA(Tracker!C2:C151)-COUNTIF(Tracker!I2:I151,"Solved")-COUNTIF(Tracker!I2:I151,"Solved with Help")-COUNTIF(Tracker!I2:I151,"Attempted")</f>
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="19" t="n">
         <f aca="false">(COUNTIF(Tracker!I2:I151,"Solved")+COUNTIF(Tracker!I2:I151,"Solved with Help"))/COUNTA(Tracker!C2:C151)</f>
-        <v>0.00666666666666667</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="18" t="n">
         <f aca="true">COUNTIFS(Tracker!K2:K151,"&lt;="&amp;TODAY(),Tracker!K2:K151,"&lt;&gt;",Tracker!L2:L151,"&lt;&gt;Yes")</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="20" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="11" t="str">
+      <c r="B12" s="18" t="str">
         <f aca="false">COUNTIFS(Tracker!D2:D151,"Easy",Tracker!I2:I151,"Solved")&amp;"/"&amp;COUNTIF(Tracker!D2:D151,"Easy")</f>
         <v>0/28</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="11" t="str">
+      <c r="A13" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="18" t="str">
         <f aca="false">COUNTIFS(Tracker!D2:D151,"Medium",Tracker!I2:I151,"Solved")&amp;"/"&amp;COUNTIF(Tracker!D2:D151,"Medium")</f>
         <v>0/101</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="11" t="str">
+      <c r="B14" s="18" t="str">
         <f aca="false">COUNTIFS(Tracker!D2:D151,"Hard",Tracker!I2:I151,"Solved")&amp;"/"&amp;COUNTIF(Tracker!D2:D151,"Hard")</f>
         <v>0/21</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="20" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="21" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="21" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="21" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="21" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="21" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="21" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="21" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="14" t="s">
+      <c r="A24" s="21" t="s">
         <v>201</v>
       </c>
     </row>

--- a/neetcode_150_tracker.xlsx
+++ b/neetcode_150_tracker.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="203">
   <si>
     <t xml:space="preserve">#</t>
   </si>
@@ -275,6 +275,12 @@
     <t xml:space="preserve">Serialize and Deserialize Binary Tree</t>
   </si>
   <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solved</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tries</t>
   </si>
   <si>
@@ -582,9 +588,6 @@
   </si>
   <si>
     <t xml:space="preserve">Total Problems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solved</t>
   </si>
   <si>
     <t xml:space="preserve">Attempted (not solved)</t>
@@ -640,7 +643,7 @@
     <numFmt numFmtId="167" formatCode="General"/>
     <numFmt numFmtId="168" formatCode="0%"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -676,11 +679,6 @@
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="0"/>
     </font>
     <font>
       <b val="true"/>
@@ -792,7 +790,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -853,15 +851,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -873,11 +867,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2776,7 +2770,7 @@
       <c r="I60" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="J60" s="15" t="n">
+      <c r="J60" s="12" t="n">
         <v>46217</v>
       </c>
       <c r="K60" s="10" t="n">
@@ -2799,11 +2793,17 @@
       <c r="D61" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E61" s="10"/>
-      <c r="F61" s="11"/>
+      <c r="E61" s="10" t="n">
+        <v>46218</v>
+      </c>
+      <c r="F61" s="11" t="s">
+        <v>84</v>
+      </c>
       <c r="G61" s="8"/>
       <c r="H61" s="8"/>
-      <c r="I61" s="11"/>
+      <c r="I61" s="11" t="s">
+        <v>85</v>
+      </c>
       <c r="J61" s="12"/>
       <c r="K61" s="10" t="str">
         <f aca="false">IF(J61="","",J61+14)</f>
@@ -2817,10 +2817,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D62" s="13" t="s">
         <v>19</v>
@@ -2843,10 +2843,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D63" s="13" t="s">
         <v>19</v>
@@ -2869,10 +2869,10 @@
         <v>63</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D64" s="14" t="s">
         <v>31</v>
@@ -2895,10 +2895,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D65" s="9" t="s">
         <v>15</v>
@@ -2921,10 +2921,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D66" s="9" t="s">
         <v>15</v>
@@ -2947,10 +2947,10 @@
         <v>66</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D67" s="13" t="s">
         <v>19</v>
@@ -2973,10 +2973,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D68" s="13" t="s">
         <v>19</v>
@@ -2999,10 +2999,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D69" s="13" t="s">
         <v>19</v>
@@ -3025,10 +3025,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D70" s="13" t="s">
         <v>19</v>
@@ -3051,23 +3051,31 @@
         <v>70</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D71" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E71" s="10"/>
-      <c r="F71" s="11"/>
+      <c r="E71" s="10" t="n">
+        <v>46219</v>
+      </c>
+      <c r="F71" s="11" t="s">
+        <v>79</v>
+      </c>
       <c r="G71" s="8"/>
       <c r="H71" s="8"/>
-      <c r="I71" s="11"/>
-      <c r="J71" s="12"/>
-      <c r="K71" s="10" t="str">
+      <c r="I71" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="J71" s="12" t="n">
+        <v>46219</v>
+      </c>
+      <c r="K71" s="10" t="n">
         <f aca="false">IF(J71="","",J71+14)</f>
-        <v/>
+        <v>46233</v>
       </c>
       <c r="L71" s="11"/>
       <c r="M71" s="8"/>
@@ -3077,10 +3085,10 @@
         <v>71</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D72" s="13" t="s">
         <v>19</v>
@@ -3103,10 +3111,10 @@
         <v>72</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D73" s="13" t="s">
         <v>19</v>
@@ -3129,10 +3137,10 @@
         <v>73</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D74" s="13" t="s">
         <v>19</v>
@@ -3155,10 +3163,10 @@
         <v>74</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D75" s="13" t="s">
         <v>19</v>
@@ -3181,10 +3189,10 @@
         <v>75</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D76" s="13" t="s">
         <v>19</v>
@@ -3207,10 +3215,10 @@
         <v>76</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D77" s="13" t="s">
         <v>19</v>
@@ -3233,10 +3241,10 @@
         <v>77</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D78" s="13" t="s">
         <v>19</v>
@@ -3259,10 +3267,10 @@
         <v>78</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D79" s="13" t="s">
         <v>19</v>
@@ -3285,10 +3293,10 @@
         <v>79</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D80" s="14" t="s">
         <v>31</v>
@@ -3311,10 +3319,10 @@
         <v>80</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D81" s="13" t="s">
         <v>19</v>
@@ -3337,10 +3345,10 @@
         <v>81</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D82" s="13" t="s">
         <v>19</v>
@@ -3363,10 +3371,10 @@
         <v>82</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D83" s="13" t="s">
         <v>19</v>
@@ -3389,10 +3397,10 @@
         <v>83</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D84" s="13" t="s">
         <v>19</v>
@@ -3415,10 +3423,10 @@
         <v>84</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D85" s="13" t="s">
         <v>19</v>
@@ -3441,10 +3449,10 @@
         <v>85</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D86" s="13" t="s">
         <v>19</v>
@@ -3467,10 +3475,10 @@
         <v>86</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D87" s="13" t="s">
         <v>19</v>
@@ -3493,10 +3501,10 @@
         <v>87</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D88" s="13" t="s">
         <v>19</v>
@@ -3519,10 +3527,10 @@
         <v>88</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D89" s="13" t="s">
         <v>19</v>
@@ -3545,10 +3553,10 @@
         <v>89</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D90" s="13" t="s">
         <v>19</v>
@@ -3571,10 +3579,10 @@
         <v>90</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D91" s="13" t="s">
         <v>19</v>
@@ -3597,10 +3605,10 @@
         <v>91</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D92" s="13" t="s">
         <v>19</v>
@@ -3623,10 +3631,10 @@
         <v>92</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D93" s="14" t="s">
         <v>31</v>
@@ -3649,10 +3657,10 @@
         <v>93</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D94" s="14" t="s">
         <v>31</v>
@@ -3675,10 +3683,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D95" s="13" t="s">
         <v>19</v>
@@ -3701,10 +3709,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D96" s="13" t="s">
         <v>19</v>
@@ -3727,10 +3735,10 @@
         <v>96</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D97" s="14" t="s">
         <v>31</v>
@@ -3753,10 +3761,10 @@
         <v>97</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D98" s="14" t="s">
         <v>31</v>
@@ -3779,10 +3787,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D99" s="13" t="s">
         <v>19</v>
@@ -3805,10 +3813,10 @@
         <v>99</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D100" s="9" t="s">
         <v>15</v>
@@ -3831,10 +3839,10 @@
         <v>100</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D101" s="9" t="s">
         <v>15</v>
@@ -3857,10 +3865,10 @@
         <v>101</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D102" s="13" t="s">
         <v>19</v>
@@ -3883,10 +3891,10 @@
         <v>102</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D103" s="13" t="s">
         <v>19</v>
@@ -3909,10 +3917,10 @@
         <v>103</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D104" s="13" t="s">
         <v>19</v>
@@ -3935,10 +3943,10 @@
         <v>104</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D105" s="13" t="s">
         <v>19</v>
@@ -3961,10 +3969,10 @@
         <v>105</v>
       </c>
       <c r="B106" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D106" s="13" t="s">
         <v>19</v>
@@ -3987,10 +3995,10 @@
         <v>106</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D107" s="13" t="s">
         <v>19</v>
@@ -4013,10 +4021,10 @@
         <v>107</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D108" s="13" t="s">
         <v>19</v>
@@ -4039,10 +4047,10 @@
         <v>108</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D109" s="13" t="s">
         <v>19</v>
@@ -4065,10 +4073,10 @@
         <v>109</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D110" s="13" t="s">
         <v>19</v>
@@ -4091,10 +4099,10 @@
         <v>110</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D111" s="13" t="s">
         <v>19</v>
@@ -4117,10 +4125,10 @@
         <v>111</v>
       </c>
       <c r="B112" s="8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D112" s="13" t="s">
         <v>19</v>
@@ -4143,10 +4151,10 @@
         <v>112</v>
       </c>
       <c r="B113" s="8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D113" s="13" t="s">
         <v>19</v>
@@ -4169,10 +4177,10 @@
         <v>113</v>
       </c>
       <c r="B114" s="8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D114" s="13" t="s">
         <v>19</v>
@@ -4195,10 +4203,10 @@
         <v>114</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D115" s="13" t="s">
         <v>19</v>
@@ -4221,10 +4229,10 @@
         <v>115</v>
       </c>
       <c r="B116" s="8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D116" s="13" t="s">
         <v>19</v>
@@ -4247,10 +4255,10 @@
         <v>116</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D117" s="13" t="s">
         <v>19</v>
@@ -4273,10 +4281,10 @@
         <v>117</v>
       </c>
       <c r="B118" s="8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D118" s="14" t="s">
         <v>31</v>
@@ -4299,10 +4307,10 @@
         <v>118</v>
       </c>
       <c r="B119" s="8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D119" s="14" t="s">
         <v>31</v>
@@ -4325,10 +4333,10 @@
         <v>119</v>
       </c>
       <c r="B120" s="8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D120" s="13" t="s">
         <v>19</v>
@@ -4351,10 +4359,10 @@
         <v>120</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D121" s="14" t="s">
         <v>31</v>
@@ -4377,10 +4385,10 @@
         <v>121</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D122" s="14" t="s">
         <v>31</v>
@@ -4403,10 +4411,10 @@
         <v>122</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D123" s="13" t="s">
         <v>19</v>
@@ -4429,10 +4437,10 @@
         <v>123</v>
       </c>
       <c r="B124" s="8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D124" s="13" t="s">
         <v>19</v>
@@ -4455,10 +4463,10 @@
         <v>124</v>
       </c>
       <c r="B125" s="8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D125" s="13" t="s">
         <v>19</v>
@@ -4481,10 +4489,10 @@
         <v>125</v>
       </c>
       <c r="B126" s="8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D126" s="13" t="s">
         <v>19</v>
@@ -4507,10 +4515,10 @@
         <v>126</v>
       </c>
       <c r="B127" s="8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D127" s="13" t="s">
         <v>19</v>
@@ -4533,10 +4541,10 @@
         <v>127</v>
       </c>
       <c r="B128" s="8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D128" s="13" t="s">
         <v>19</v>
@@ -4559,10 +4567,10 @@
         <v>128</v>
       </c>
       <c r="B129" s="8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D129" s="13" t="s">
         <v>19</v>
@@ -4585,10 +4593,10 @@
         <v>129</v>
       </c>
       <c r="B130" s="8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D130" s="13" t="s">
         <v>19</v>
@@ -4611,10 +4619,10 @@
         <v>130</v>
       </c>
       <c r="B131" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D131" s="13" t="s">
         <v>19</v>
@@ -4637,10 +4645,10 @@
         <v>131</v>
       </c>
       <c r="B132" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D132" s="13" t="s">
         <v>19</v>
@@ -4663,10 +4671,10 @@
         <v>132</v>
       </c>
       <c r="B133" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D133" s="13" t="s">
         <v>19</v>
@@ -4689,10 +4697,10 @@
         <v>133</v>
       </c>
       <c r="B134" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D134" s="9" t="s">
         <v>15</v>
@@ -4715,10 +4723,10 @@
         <v>134</v>
       </c>
       <c r="B135" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D135" s="13" t="s">
         <v>19</v>
@@ -4741,10 +4749,10 @@
         <v>135</v>
       </c>
       <c r="B136" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D136" s="14" t="s">
         <v>31</v>
@@ -4767,10 +4775,10 @@
         <v>136</v>
       </c>
       <c r="B137" s="8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D137" s="13" t="s">
         <v>19</v>
@@ -4793,10 +4801,10 @@
         <v>137</v>
       </c>
       <c r="B138" s="8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D138" s="13" t="s">
         <v>19</v>
@@ -4819,10 +4827,10 @@
         <v>138</v>
       </c>
       <c r="B139" s="8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D139" s="13" t="s">
         <v>19</v>
@@ -4845,10 +4853,10 @@
         <v>139</v>
       </c>
       <c r="B140" s="8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D140" s="9" t="s">
         <v>15</v>
@@ -4871,10 +4879,10 @@
         <v>140</v>
       </c>
       <c r="B141" s="8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D141" s="9" t="s">
         <v>15</v>
@@ -4897,10 +4905,10 @@
         <v>141</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D142" s="13" t="s">
         <v>19</v>
@@ -4923,10 +4931,10 @@
         <v>142</v>
       </c>
       <c r="B143" s="8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D143" s="13" t="s">
         <v>19</v>
@@ -4949,10 +4957,10 @@
         <v>143</v>
       </c>
       <c r="B144" s="8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C144" s="8" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D144" s="13" t="s">
         <v>19</v>
@@ -4975,10 +4983,10 @@
         <v>144</v>
       </c>
       <c r="B145" s="8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D145" s="9" t="s">
         <v>15</v>
@@ -5001,10 +5009,10 @@
         <v>145</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C146" s="8" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D146" s="9" t="s">
         <v>15</v>
@@ -5027,10 +5035,10 @@
         <v>146</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D147" s="9" t="s">
         <v>15</v>
@@ -5053,10 +5061,10 @@
         <v>147</v>
       </c>
       <c r="B148" s="8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D148" s="9" t="s">
         <v>15</v>
@@ -5079,10 +5087,10 @@
         <v>148</v>
       </c>
       <c r="B149" s="8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D149" s="9" t="s">
         <v>15</v>
@@ -5105,10 +5113,10 @@
         <v>149</v>
       </c>
       <c r="B150" s="8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D150" s="13" t="s">
         <v>19</v>
@@ -5131,10 +5139,10 @@
         <v>150</v>
       </c>
       <c r="B151" s="8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D151" s="13" t="s">
         <v>19</v>
@@ -5209,148 +5217,148 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
-        <v>185</v>
+      <c r="A1" s="15" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="B3" s="18" t="n">
+      <c r="A3" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="B3" s="17" t="n">
         <f aca="false">COUNTA(Tracker!C2:C151)</f>
         <v>150</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="B4" s="18" t="n">
+      <c r="A4" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="B4" s="17" t="n">
         <f aca="false">COUNTIF(Tracker!I2:I151,"Solved")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="B5" s="18" t="n">
+      <c r="B5" s="17" t="n">
         <f aca="false">COUNTIF(Tracker!I2:I151,"Solved with Help")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="B6" s="18" t="n">
+      <c r="A6" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B6" s="17" t="n">
         <f aca="false">COUNTIF(Tracker!I2:I151,"Attempted")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="B7" s="18" t="n">
+      <c r="A7" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="B7" s="17" t="n">
         <f aca="false">COUNTA(Tracker!C2:C151)-COUNTIF(Tracker!I2:I151,"Solved")-COUNTIF(Tracker!I2:I151,"Solved with Help")-COUNTIF(Tracker!I2:I151,"Attempted")</f>
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
-        <v>190</v>
-      </c>
-      <c r="B8" s="19" t="n">
+      <c r="A8" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="B8" s="18" t="n">
         <f aca="false">(COUNTIF(Tracker!I2:I151,"Solved")+COUNTIF(Tracker!I2:I151,"Solved with Help"))/COUNTA(Tracker!C2:C151)</f>
-        <v>0.02</v>
+        <v>0.0333333333333333</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="B9" s="18" t="n">
+      <c r="A9" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="B9" s="17" t="n">
         <f aca="true">COUNTIFS(Tracker!K2:K151,"&lt;="&amp;TODAY(),Tracker!K2:K151,"&lt;&gt;",Tracker!L2:L151,"&lt;&gt;Yes")</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
-        <v>192</v>
+      <c r="A11" s="19" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="18" t="str">
+      <c r="B12" s="17" t="str">
         <f aca="false">COUNTIFS(Tracker!D2:D151,"Easy",Tracker!I2:I151,"Solved")&amp;"/"&amp;COUNTIF(Tracker!D2:D151,"Easy")</f>
         <v>0/28</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="18" t="str">
+      <c r="A13" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="17" t="str">
         <f aca="false">COUNTIFS(Tracker!D2:D151,"Medium",Tracker!I2:I151,"Solved")&amp;"/"&amp;COUNTIF(Tracker!D2:D151,"Medium")</f>
         <v>0/101</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="18" t="str">
+      <c r="B14" s="17" t="str">
         <f aca="false">COUNTIFS(Tracker!D2:D151,"Hard",Tracker!I2:I151,"Solved")&amp;"/"&amp;COUNTIF(Tracker!D2:D151,"Hard")</f>
-        <v>0/21</v>
+        <v>1/21</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="20" t="s">
-        <v>193</v>
+      <c r="A16" s="19" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="21" t="s">
-        <v>194</v>
+      <c r="A17" s="20" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="21" t="s">
-        <v>195</v>
+      <c r="A18" s="20" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="21" t="s">
-        <v>196</v>
+      <c r="A19" s="20" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="21" t="s">
-        <v>197</v>
+      <c r="A20" s="20" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="21" t="s">
-        <v>198</v>
+      <c r="A21" s="20" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="21" t="s">
-        <v>199</v>
+      <c r="A22" s="20" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="21" t="s">
-        <v>200</v>
+      <c r="A23" s="20" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="21" t="s">
-        <v>201</v>
+      <c r="A24" s="20" t="s">
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/neetcode_150_tracker.xlsx
+++ b/neetcode_150_tracker.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="204">
   <si>
     <t xml:space="preserve">#</t>
   </si>
@@ -263,24 +263,24 @@
     <t xml:space="preserve">No</t>
   </si>
   <si>
+    <t xml:space="preserve">Solved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Construct Binary Tree from Preorder and Inorder Traversal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binary Tree Maximum Path Sum</t>
+  </si>
+  <si>
     <t xml:space="preserve">Solved with Help</t>
   </si>
   <si>
-    <t xml:space="preserve">Construct Binary Tree from Preorder and Inorder Traversal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binary Tree Maximum Path Sum</t>
-  </si>
-  <si>
     <t xml:space="preserve">Serialize and Deserialize Binary Tree</t>
   </si>
   <si>
     <t xml:space="preserve">Yes</t>
   </si>
   <si>
-    <t xml:space="preserve">Solved</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tries</t>
   </si>
   <si>
@@ -336,6 +336,9 @@
   </si>
   <si>
     <t xml:space="preserve">Word Search</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28,Jul,2026</t>
   </si>
   <si>
     <t xml:space="preserve">Palindrome Partitioning</t>
@@ -2702,12 +2705,10 @@
       <c r="I58" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="J58" s="12" t="n">
-        <v>46213</v>
-      </c>
-      <c r="K58" s="10" t="n">
+      <c r="J58" s="12"/>
+      <c r="K58" s="10" t="str">
         <f aca="false">IF(J58="","",J58+14)</f>
-        <v>46227</v>
+        <v/>
       </c>
       <c r="L58" s="11"/>
       <c r="M58" s="8"/>
@@ -2736,12 +2737,10 @@
       <c r="I59" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="J59" s="12" t="n">
-        <v>46214</v>
-      </c>
-      <c r="K59" s="10" t="n">
+      <c r="J59" s="12"/>
+      <c r="K59" s="10" t="str">
         <f aca="false">IF(J59="","",J59+14)</f>
-        <v>46228</v>
+        <v/>
       </c>
       <c r="L59" s="11"/>
       <c r="M59" s="8"/>
@@ -2768,7 +2767,7 @@
       <c r="G60" s="8"/>
       <c r="H60" s="8"/>
       <c r="I60" s="11" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J60" s="12" t="n">
         <v>46217</v>
@@ -2788,7 +2787,7 @@
         <v>66</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D61" s="14" t="s">
         <v>31</v>
@@ -2797,12 +2796,12 @@
         <v>46218</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G61" s="8"/>
       <c r="H61" s="8"/>
       <c r="I61" s="11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="J61" s="12"/>
       <c r="K61" s="10" t="str">
@@ -3070,12 +3069,10 @@
       <c r="I71" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="J71" s="12" t="n">
-        <v>46219</v>
-      </c>
-      <c r="K71" s="10" t="n">
+      <c r="J71" s="12"/>
+      <c r="K71" s="10" t="str">
         <f aca="false">IF(J71="","",J71+14)</f>
-        <v>46233</v>
+        <v/>
       </c>
       <c r="L71" s="11"/>
       <c r="M71" s="8"/>
@@ -3119,15 +3116,23 @@
       <c r="D73" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E73" s="10"/>
-      <c r="F73" s="11"/>
+      <c r="E73" s="10" t="n">
+        <v>46221</v>
+      </c>
+      <c r="F73" s="11" t="s">
+        <v>79</v>
+      </c>
       <c r="G73" s="8"/>
       <c r="H73" s="8"/>
-      <c r="I73" s="11"/>
-      <c r="J73" s="12"/>
-      <c r="K73" s="10" t="str">
+      <c r="I73" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="J73" s="12" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K73" s="10" t="n">
         <f aca="false">IF(J73="","",J73+14)</f>
-        <v/>
+        <v>46235</v>
       </c>
       <c r="L73" s="11"/>
       <c r="M73" s="8"/>
@@ -3223,15 +3228,23 @@
       <c r="D77" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E77" s="10"/>
-      <c r="F77" s="11"/>
+      <c r="E77" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="F77" s="11" t="s">
+        <v>79</v>
+      </c>
       <c r="G77" s="8"/>
       <c r="H77" s="8"/>
-      <c r="I77" s="11"/>
-      <c r="J77" s="12"/>
-      <c r="K77" s="10" t="str">
+      <c r="I77" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="J77" s="12" t="n">
+        <v>46231</v>
+      </c>
+      <c r="K77" s="10" t="n">
         <f aca="false">IF(J77="","",J77+14)</f>
-        <v/>
+        <v>46245</v>
       </c>
       <c r="L77" s="11"/>
       <c r="M77" s="8"/>
@@ -3244,7 +3257,7 @@
         <v>98</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D78" s="13" t="s">
         <v>19</v>
@@ -3270,7 +3283,7 @@
         <v>98</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D79" s="13" t="s">
         <v>19</v>
@@ -3296,7 +3309,7 @@
         <v>98</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D80" s="14" t="s">
         <v>31</v>
@@ -3319,10 +3332,10 @@
         <v>80</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D81" s="13" t="s">
         <v>19</v>
@@ -3345,10 +3358,10 @@
         <v>81</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D82" s="13" t="s">
         <v>19</v>
@@ -3371,10 +3384,10 @@
         <v>82</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D83" s="13" t="s">
         <v>19</v>
@@ -3397,10 +3410,10 @@
         <v>83</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D84" s="13" t="s">
         <v>19</v>
@@ -3423,10 +3436,10 @@
         <v>84</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D85" s="13" t="s">
         <v>19</v>
@@ -3449,10 +3462,10 @@
         <v>85</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D86" s="13" t="s">
         <v>19</v>
@@ -3475,10 +3488,10 @@
         <v>86</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D87" s="13" t="s">
         <v>19</v>
@@ -3501,10 +3514,10 @@
         <v>87</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D88" s="13" t="s">
         <v>19</v>
@@ -3527,10 +3540,10 @@
         <v>88</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D89" s="13" t="s">
         <v>19</v>
@@ -3553,10 +3566,10 @@
         <v>89</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D90" s="13" t="s">
         <v>19</v>
@@ -3579,10 +3592,10 @@
         <v>90</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D91" s="13" t="s">
         <v>19</v>
@@ -3605,10 +3618,10 @@
         <v>91</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D92" s="13" t="s">
         <v>19</v>
@@ -3631,10 +3644,10 @@
         <v>92</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D93" s="14" t="s">
         <v>31</v>
@@ -3657,10 +3670,10 @@
         <v>93</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D94" s="14" t="s">
         <v>31</v>
@@ -3683,10 +3696,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D95" s="13" t="s">
         <v>19</v>
@@ -3709,10 +3722,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D96" s="13" t="s">
         <v>19</v>
@@ -3735,10 +3748,10 @@
         <v>96</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D97" s="14" t="s">
         <v>31</v>
@@ -3761,10 +3774,10 @@
         <v>97</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D98" s="14" t="s">
         <v>31</v>
@@ -3787,10 +3800,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D99" s="13" t="s">
         <v>19</v>
@@ -3813,10 +3826,10 @@
         <v>99</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D100" s="9" t="s">
         <v>15</v>
@@ -3839,10 +3852,10 @@
         <v>100</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D101" s="9" t="s">
         <v>15</v>
@@ -3865,10 +3878,10 @@
         <v>101</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D102" s="13" t="s">
         <v>19</v>
@@ -3891,10 +3904,10 @@
         <v>102</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D103" s="13" t="s">
         <v>19</v>
@@ -3917,10 +3930,10 @@
         <v>103</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D104" s="13" t="s">
         <v>19</v>
@@ -3943,10 +3956,10 @@
         <v>104</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D105" s="13" t="s">
         <v>19</v>
@@ -3969,10 +3982,10 @@
         <v>105</v>
       </c>
       <c r="B106" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D106" s="13" t="s">
         <v>19</v>
@@ -3995,10 +4008,10 @@
         <v>106</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D107" s="13" t="s">
         <v>19</v>
@@ -4021,10 +4034,10 @@
         <v>107</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D108" s="13" t="s">
         <v>19</v>
@@ -4047,10 +4060,10 @@
         <v>108</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D109" s="13" t="s">
         <v>19</v>
@@ -4073,10 +4086,10 @@
         <v>109</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D110" s="13" t="s">
         <v>19</v>
@@ -4099,10 +4112,10 @@
         <v>110</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D111" s="13" t="s">
         <v>19</v>
@@ -4125,10 +4138,10 @@
         <v>111</v>
       </c>
       <c r="B112" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D112" s="13" t="s">
         <v>19</v>
@@ -4151,10 +4164,10 @@
         <v>112</v>
       </c>
       <c r="B113" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D113" s="13" t="s">
         <v>19</v>
@@ -4177,10 +4190,10 @@
         <v>113</v>
       </c>
       <c r="B114" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D114" s="13" t="s">
         <v>19</v>
@@ -4203,10 +4216,10 @@
         <v>114</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D115" s="13" t="s">
         <v>19</v>
@@ -4229,10 +4242,10 @@
         <v>115</v>
       </c>
       <c r="B116" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D116" s="13" t="s">
         <v>19</v>
@@ -4255,10 +4268,10 @@
         <v>116</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D117" s="13" t="s">
         <v>19</v>
@@ -4281,10 +4294,10 @@
         <v>117</v>
       </c>
       <c r="B118" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D118" s="14" t="s">
         <v>31</v>
@@ -4307,10 +4320,10 @@
         <v>118</v>
       </c>
       <c r="B119" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D119" s="14" t="s">
         <v>31</v>
@@ -4333,10 +4346,10 @@
         <v>119</v>
       </c>
       <c r="B120" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D120" s="13" t="s">
         <v>19</v>
@@ -4359,10 +4372,10 @@
         <v>120</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D121" s="14" t="s">
         <v>31</v>
@@ -4385,10 +4398,10 @@
         <v>121</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D122" s="14" t="s">
         <v>31</v>
@@ -4411,10 +4424,10 @@
         <v>122</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D123" s="13" t="s">
         <v>19</v>
@@ -4437,10 +4450,10 @@
         <v>123</v>
       </c>
       <c r="B124" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D124" s="13" t="s">
         <v>19</v>
@@ -4463,10 +4476,10 @@
         <v>124</v>
       </c>
       <c r="B125" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D125" s="13" t="s">
         <v>19</v>
@@ -4489,10 +4502,10 @@
         <v>125</v>
       </c>
       <c r="B126" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D126" s="13" t="s">
         <v>19</v>
@@ -4515,10 +4528,10 @@
         <v>126</v>
       </c>
       <c r="B127" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D127" s="13" t="s">
         <v>19</v>
@@ -4541,10 +4554,10 @@
         <v>127</v>
       </c>
       <c r="B128" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D128" s="13" t="s">
         <v>19</v>
@@ -4567,10 +4580,10 @@
         <v>128</v>
       </c>
       <c r="B129" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D129" s="13" t="s">
         <v>19</v>
@@ -4593,10 +4606,10 @@
         <v>129</v>
       </c>
       <c r="B130" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D130" s="13" t="s">
         <v>19</v>
@@ -4619,10 +4632,10 @@
         <v>130</v>
       </c>
       <c r="B131" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D131" s="13" t="s">
         <v>19</v>
@@ -4645,10 +4658,10 @@
         <v>131</v>
       </c>
       <c r="B132" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D132" s="13" t="s">
         <v>19</v>
@@ -4671,10 +4684,10 @@
         <v>132</v>
       </c>
       <c r="B133" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D133" s="13" t="s">
         <v>19</v>
@@ -4697,10 +4710,10 @@
         <v>133</v>
       </c>
       <c r="B134" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D134" s="9" t="s">
         <v>15</v>
@@ -4723,10 +4736,10 @@
         <v>134</v>
       </c>
       <c r="B135" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D135" s="13" t="s">
         <v>19</v>
@@ -4749,10 +4762,10 @@
         <v>135</v>
       </c>
       <c r="B136" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D136" s="14" t="s">
         <v>31</v>
@@ -4775,10 +4788,10 @@
         <v>136</v>
       </c>
       <c r="B137" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D137" s="13" t="s">
         <v>19</v>
@@ -4801,10 +4814,10 @@
         <v>137</v>
       </c>
       <c r="B138" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D138" s="13" t="s">
         <v>19</v>
@@ -4827,10 +4840,10 @@
         <v>138</v>
       </c>
       <c r="B139" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D139" s="13" t="s">
         <v>19</v>
@@ -4853,10 +4866,10 @@
         <v>139</v>
       </c>
       <c r="B140" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D140" s="9" t="s">
         <v>15</v>
@@ -4879,10 +4892,10 @@
         <v>140</v>
       </c>
       <c r="B141" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D141" s="9" t="s">
         <v>15</v>
@@ -4905,10 +4918,10 @@
         <v>141</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D142" s="13" t="s">
         <v>19</v>
@@ -4931,10 +4944,10 @@
         <v>142</v>
       </c>
       <c r="B143" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D143" s="13" t="s">
         <v>19</v>
@@ -4957,10 +4970,10 @@
         <v>143</v>
       </c>
       <c r="B144" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C144" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D144" s="13" t="s">
         <v>19</v>
@@ -4983,10 +4996,10 @@
         <v>144</v>
       </c>
       <c r="B145" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D145" s="9" t="s">
         <v>15</v>
@@ -5009,10 +5022,10 @@
         <v>145</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C146" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D146" s="9" t="s">
         <v>15</v>
@@ -5035,10 +5048,10 @@
         <v>146</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D147" s="9" t="s">
         <v>15</v>
@@ -5061,10 +5074,10 @@
         <v>147</v>
       </c>
       <c r="B148" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D148" s="9" t="s">
         <v>15</v>
@@ -5087,10 +5100,10 @@
         <v>148</v>
       </c>
       <c r="B149" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D149" s="9" t="s">
         <v>15</v>
@@ -5113,10 +5126,10 @@
         <v>149</v>
       </c>
       <c r="B150" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D150" s="13" t="s">
         <v>19</v>
@@ -5139,10 +5152,10 @@
         <v>150</v>
       </c>
       <c r="B151" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D151" s="13" t="s">
         <v>19</v>
@@ -5218,12 +5231,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B3" s="17" t="n">
         <f aca="false">COUNTA(Tracker!C2:C151)</f>
@@ -5232,25 +5245,25 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B4" s="17" t="n">
         <f aca="false">COUNTIF(Tracker!I2:I151,"Solved")</f>
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B5" s="17" t="n">
         <f aca="false">COUNTIF(Tracker!I2:I151,"Solved with Help")</f>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B6" s="17" t="n">
         <f aca="false">COUNTIF(Tracker!I2:I151,"Attempted")</f>
@@ -5259,34 +5272,34 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B7" s="17" t="n">
         <f aca="false">COUNTA(Tracker!C2:C151)-COUNTIF(Tracker!I2:I151,"Solved")-COUNTIF(Tracker!I2:I151,"Solved with Help")-COUNTIF(Tracker!I2:I151,"Attempted")</f>
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B8" s="18" t="n">
         <f aca="false">(COUNTIF(Tracker!I2:I151,"Solved")+COUNTIF(Tracker!I2:I151,"Solved with Help"))/COUNTA(Tracker!C2:C151)</f>
-        <v>0.0333333333333333</v>
+        <v>0.0466666666666667</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B9" s="17" t="n">
         <f aca="true">COUNTIFS(Tracker!K2:K151,"&lt;="&amp;TODAY(),Tracker!K2:K151,"&lt;&gt;",Tracker!L2:L151,"&lt;&gt;Yes")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5304,7 +5317,7 @@
       </c>
       <c r="B13" s="17" t="str">
         <f aca="false">COUNTIFS(Tracker!D2:D151,"Medium",Tracker!I2:I151,"Solved")&amp;"/"&amp;COUNTIF(Tracker!D2:D151,"Medium")</f>
-        <v>0/101</v>
+        <v>3/101</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5313,52 +5326,52 @@
       </c>
       <c r="B14" s="17" t="str">
         <f aca="false">COUNTIFS(Tracker!D2:D151,"Hard",Tracker!I2:I151,"Solved")&amp;"/"&amp;COUNTIF(Tracker!D2:D151,"Hard")</f>
-        <v>1/21</v>
+        <v>2/21</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="20" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="20" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="20" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>

--- a/neetcode_150_tracker.xlsx
+++ b/neetcode_150_tracker.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Tracker" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="203">
   <si>
     <t xml:space="preserve">#</t>
   </si>
@@ -336,9 +336,6 @@
   </si>
   <si>
     <t xml:space="preserve">Word Search</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28,Jul,2026</t>
   </si>
   <si>
     <t xml:space="preserve">Palindrome Partitioning</t>
@@ -2824,15 +2821,22 @@
       <c r="D62" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E62" s="10"/>
-      <c r="F62" s="11"/>
+      <c r="E62" s="10" t="n">
+        <v>46233</v>
+      </c>
+      <c r="F62" s="11" t="s">
+        <v>79</v>
+      </c>
       <c r="G62" s="8"/>
       <c r="H62" s="8"/>
-      <c r="I62" s="11"/>
-      <c r="J62" s="12"/>
-      <c r="K62" s="10" t="str">
-        <f aca="false">IF(J62="","",J62+14)</f>
-        <v/>
+      <c r="I62" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="J62" s="12" t="n">
+        <v>46221</v>
+      </c>
+      <c r="K62" s="10" t="n">
+        <v>46247</v>
       </c>
       <c r="L62" s="11"/>
       <c r="M62" s="8"/>
@@ -2856,10 +2860,7 @@
       <c r="H63" s="8"/>
       <c r="I63" s="11"/>
       <c r="J63" s="12"/>
-      <c r="K63" s="10" t="str">
-        <f aca="false">IF(J63="","",J63+14)</f>
-        <v/>
-      </c>
+      <c r="K63" s="10"/>
       <c r="L63" s="11"/>
       <c r="M63" s="8"/>
     </row>
@@ -2882,10 +2883,7 @@
       <c r="H64" s="8"/>
       <c r="I64" s="11"/>
       <c r="J64" s="12"/>
-      <c r="K64" s="10" t="str">
-        <f aca="false">IF(J64="","",J64+14)</f>
-        <v/>
-      </c>
+      <c r="K64" s="10"/>
       <c r="L64" s="11"/>
       <c r="M64" s="8"/>
     </row>
@@ -3228,8 +3226,8 @@
       <c r="D77" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E77" s="10" t="s">
-        <v>105</v>
+      <c r="E77" s="10" t="n">
+        <v>46231</v>
       </c>
       <c r="F77" s="11" t="s">
         <v>79</v>
@@ -3257,7 +3255,7 @@
         <v>98</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D78" s="13" t="s">
         <v>19</v>
@@ -3283,7 +3281,7 @@
         <v>98</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D79" s="13" t="s">
         <v>19</v>
@@ -3309,7 +3307,7 @@
         <v>98</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D80" s="14" t="s">
         <v>31</v>
@@ -3332,10 +3330,10 @@
         <v>80</v>
       </c>
       <c r="B81" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C81" s="8" t="s">
         <v>109</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>110</v>
       </c>
       <c r="D81" s="13" t="s">
         <v>19</v>
@@ -3358,10 +3356,10 @@
         <v>81</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D82" s="13" t="s">
         <v>19</v>
@@ -3384,10 +3382,10 @@
         <v>82</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D83" s="13" t="s">
         <v>19</v>
@@ -3410,10 +3408,10 @@
         <v>83</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D84" s="13" t="s">
         <v>19</v>
@@ -3436,10 +3434,10 @@
         <v>84</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D85" s="13" t="s">
         <v>19</v>
@@ -3462,10 +3460,10 @@
         <v>85</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D86" s="13" t="s">
         <v>19</v>
@@ -3488,10 +3486,10 @@
         <v>86</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D87" s="13" t="s">
         <v>19</v>
@@ -3514,10 +3512,10 @@
         <v>87</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D88" s="13" t="s">
         <v>19</v>
@@ -3540,10 +3538,10 @@
         <v>88</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D89" s="13" t="s">
         <v>19</v>
@@ -3566,10 +3564,10 @@
         <v>89</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D90" s="13" t="s">
         <v>19</v>
@@ -3592,10 +3590,10 @@
         <v>90</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D91" s="13" t="s">
         <v>19</v>
@@ -3618,10 +3616,10 @@
         <v>91</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D92" s="13" t="s">
         <v>19</v>
@@ -3644,10 +3642,10 @@
         <v>92</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D93" s="14" t="s">
         <v>31</v>
@@ -3670,10 +3668,10 @@
         <v>93</v>
       </c>
       <c r="B94" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C94" s="8" t="s">
         <v>123</v>
-      </c>
-      <c r="C94" s="8" t="s">
-        <v>124</v>
       </c>
       <c r="D94" s="14" t="s">
         <v>31</v>
@@ -3696,10 +3694,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D95" s="13" t="s">
         <v>19</v>
@@ -3722,10 +3720,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D96" s="13" t="s">
         <v>19</v>
@@ -3748,10 +3746,10 @@
         <v>96</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D97" s="14" t="s">
         <v>31</v>
@@ -3774,10 +3772,10 @@
         <v>97</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D98" s="14" t="s">
         <v>31</v>
@@ -3800,10 +3798,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D99" s="13" t="s">
         <v>19</v>
@@ -3826,10 +3824,10 @@
         <v>99</v>
       </c>
       <c r="B100" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C100" s="8" t="s">
         <v>130</v>
-      </c>
-      <c r="C100" s="8" t="s">
-        <v>131</v>
       </c>
       <c r="D100" s="9" t="s">
         <v>15</v>
@@ -3852,10 +3850,10 @@
         <v>100</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D101" s="9" t="s">
         <v>15</v>
@@ -3878,10 +3876,10 @@
         <v>101</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D102" s="13" t="s">
         <v>19</v>
@@ -3904,10 +3902,10 @@
         <v>102</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D103" s="13" t="s">
         <v>19</v>
@@ -3930,10 +3928,10 @@
         <v>103</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D104" s="13" t="s">
         <v>19</v>
@@ -3956,10 +3954,10 @@
         <v>104</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D105" s="13" t="s">
         <v>19</v>
@@ -3982,10 +3980,10 @@
         <v>105</v>
       </c>
       <c r="B106" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D106" s="13" t="s">
         <v>19</v>
@@ -4008,10 +4006,10 @@
         <v>106</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D107" s="13" t="s">
         <v>19</v>
@@ -4034,10 +4032,10 @@
         <v>107</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D108" s="13" t="s">
         <v>19</v>
@@ -4060,10 +4058,10 @@
         <v>108</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D109" s="13" t="s">
         <v>19</v>
@@ -4086,10 +4084,10 @@
         <v>109</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D110" s="13" t="s">
         <v>19</v>
@@ -4112,10 +4110,10 @@
         <v>110</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D111" s="13" t="s">
         <v>19</v>
@@ -4138,10 +4136,10 @@
         <v>111</v>
       </c>
       <c r="B112" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C112" s="8" t="s">
         <v>143</v>
-      </c>
-      <c r="C112" s="8" t="s">
-        <v>144</v>
       </c>
       <c r="D112" s="13" t="s">
         <v>19</v>
@@ -4164,10 +4162,10 @@
         <v>112</v>
       </c>
       <c r="B113" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D113" s="13" t="s">
         <v>19</v>
@@ -4190,10 +4188,10 @@
         <v>113</v>
       </c>
       <c r="B114" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D114" s="13" t="s">
         <v>19</v>
@@ -4216,10 +4214,10 @@
         <v>114</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D115" s="13" t="s">
         <v>19</v>
@@ -4242,10 +4240,10 @@
         <v>115</v>
       </c>
       <c r="B116" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D116" s="13" t="s">
         <v>19</v>
@@ -4268,10 +4266,10 @@
         <v>116</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D117" s="13" t="s">
         <v>19</v>
@@ -4294,10 +4292,10 @@
         <v>117</v>
       </c>
       <c r="B118" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D118" s="14" t="s">
         <v>31</v>
@@ -4320,10 +4318,10 @@
         <v>118</v>
       </c>
       <c r="B119" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D119" s="14" t="s">
         <v>31</v>
@@ -4346,10 +4344,10 @@
         <v>119</v>
       </c>
       <c r="B120" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D120" s="13" t="s">
         <v>19</v>
@@ -4372,10 +4370,10 @@
         <v>120</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D121" s="14" t="s">
         <v>31</v>
@@ -4398,10 +4396,10 @@
         <v>121</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D122" s="14" t="s">
         <v>31</v>
@@ -4424,10 +4422,10 @@
         <v>122</v>
       </c>
       <c r="B123" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C123" s="8" t="s">
         <v>155</v>
-      </c>
-      <c r="C123" s="8" t="s">
-        <v>156</v>
       </c>
       <c r="D123" s="13" t="s">
         <v>19</v>
@@ -4450,10 +4448,10 @@
         <v>123</v>
       </c>
       <c r="B124" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D124" s="13" t="s">
         <v>19</v>
@@ -4476,10 +4474,10 @@
         <v>124</v>
       </c>
       <c r="B125" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D125" s="13" t="s">
         <v>19</v>
@@ -4502,10 +4500,10 @@
         <v>125</v>
       </c>
       <c r="B126" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D126" s="13" t="s">
         <v>19</v>
@@ -4528,10 +4526,10 @@
         <v>126</v>
       </c>
       <c r="B127" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D127" s="13" t="s">
         <v>19</v>
@@ -4554,10 +4552,10 @@
         <v>127</v>
       </c>
       <c r="B128" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D128" s="13" t="s">
         <v>19</v>
@@ -4580,10 +4578,10 @@
         <v>128</v>
       </c>
       <c r="B129" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D129" s="13" t="s">
         <v>19</v>
@@ -4606,10 +4604,10 @@
         <v>129</v>
       </c>
       <c r="B130" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D130" s="13" t="s">
         <v>19</v>
@@ -4632,10 +4630,10 @@
         <v>130</v>
       </c>
       <c r="B131" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="C131" s="8" t="s">
         <v>164</v>
-      </c>
-      <c r="C131" s="8" t="s">
-        <v>165</v>
       </c>
       <c r="D131" s="13" t="s">
         <v>19</v>
@@ -4658,10 +4656,10 @@
         <v>131</v>
       </c>
       <c r="B132" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D132" s="13" t="s">
         <v>19</v>
@@ -4684,10 +4682,10 @@
         <v>132</v>
       </c>
       <c r="B133" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D133" s="13" t="s">
         <v>19</v>
@@ -4710,10 +4708,10 @@
         <v>133</v>
       </c>
       <c r="B134" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D134" s="9" t="s">
         <v>15</v>
@@ -4736,10 +4734,10 @@
         <v>134</v>
       </c>
       <c r="B135" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D135" s="13" t="s">
         <v>19</v>
@@ -4762,10 +4760,10 @@
         <v>135</v>
       </c>
       <c r="B136" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D136" s="14" t="s">
         <v>31</v>
@@ -4788,10 +4786,10 @@
         <v>136</v>
       </c>
       <c r="B137" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="C137" s="8" t="s">
         <v>171</v>
-      </c>
-      <c r="C137" s="8" t="s">
-        <v>172</v>
       </c>
       <c r="D137" s="13" t="s">
         <v>19</v>
@@ -4814,10 +4812,10 @@
         <v>137</v>
       </c>
       <c r="B138" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D138" s="13" t="s">
         <v>19</v>
@@ -4840,10 +4838,10 @@
         <v>138</v>
       </c>
       <c r="B139" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D139" s="13" t="s">
         <v>19</v>
@@ -4866,10 +4864,10 @@
         <v>139</v>
       </c>
       <c r="B140" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D140" s="9" t="s">
         <v>15</v>
@@ -4892,10 +4890,10 @@
         <v>140</v>
       </c>
       <c r="B141" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D141" s="9" t="s">
         <v>15</v>
@@ -4918,10 +4916,10 @@
         <v>141</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D142" s="13" t="s">
         <v>19</v>
@@ -4944,10 +4942,10 @@
         <v>142</v>
       </c>
       <c r="B143" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D143" s="13" t="s">
         <v>19</v>
@@ -4970,10 +4968,10 @@
         <v>143</v>
       </c>
       <c r="B144" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C144" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D144" s="13" t="s">
         <v>19</v>
@@ -4996,10 +4994,10 @@
         <v>144</v>
       </c>
       <c r="B145" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="C145" s="8" t="s">
         <v>180</v>
-      </c>
-      <c r="C145" s="8" t="s">
-        <v>181</v>
       </c>
       <c r="D145" s="9" t="s">
         <v>15</v>
@@ -5022,10 +5020,10 @@
         <v>145</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C146" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D146" s="9" t="s">
         <v>15</v>
@@ -5048,10 +5046,10 @@
         <v>146</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D147" s="9" t="s">
         <v>15</v>
@@ -5074,10 +5072,10 @@
         <v>147</v>
       </c>
       <c r="B148" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D148" s="9" t="s">
         <v>15</v>
@@ -5100,10 +5098,10 @@
         <v>148</v>
       </c>
       <c r="B149" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D149" s="9" t="s">
         <v>15</v>
@@ -5126,10 +5124,10 @@
         <v>149</v>
       </c>
       <c r="B150" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D150" s="13" t="s">
         <v>19</v>
@@ -5152,10 +5150,10 @@
         <v>150</v>
       </c>
       <c r="B151" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D151" s="13" t="s">
         <v>19</v>
@@ -5231,12 +5229,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B3" s="17" t="n">
         <f aca="false">COUNTA(Tracker!C2:C151)</f>
@@ -5258,12 +5256,12 @@
       </c>
       <c r="B5" s="17" t="n">
         <f aca="false">COUNTIF(Tracker!I2:I151,"Solved with Help")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B6" s="17" t="n">
         <f aca="false">COUNTIF(Tracker!I2:I151,"Attempted")</f>
@@ -5272,25 +5270,25 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B7" s="17" t="n">
         <f aca="false">COUNTA(Tracker!C2:C151)-COUNTIF(Tracker!I2:I151,"Solved")-COUNTIF(Tracker!I2:I151,"Solved with Help")-COUNTIF(Tracker!I2:I151,"Attempted")</f>
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B8" s="18" t="n">
         <f aca="false">(COUNTIF(Tracker!I2:I151,"Solved")+COUNTIF(Tracker!I2:I151,"Solved with Help"))/COUNTA(Tracker!C2:C151)</f>
-        <v>0.0466666666666667</v>
+        <v>0.0533333333333333</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B9" s="17" t="n">
         <f aca="true">COUNTIFS(Tracker!K2:K151,"&lt;="&amp;TODAY(),Tracker!K2:K151,"&lt;&gt;",Tracker!L2:L151,"&lt;&gt;Yes")</f>
@@ -5299,7 +5297,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5331,47 +5329,47 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="20" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/neetcode_150_tracker.xlsx
+++ b/neetcode_150_tracker.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Tracker" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="203">
   <si>
     <t xml:space="preserve">#</t>
   </si>
@@ -2836,7 +2836,8 @@
         <v>46221</v>
       </c>
       <c r="K62" s="10" t="n">
-        <v>46247</v>
+        <f aca="false">IF(J62="","",J62+14)</f>
+        <v>46235</v>
       </c>
       <c r="L62" s="11"/>
       <c r="M62" s="8"/>
@@ -2854,13 +2855,24 @@
       <c r="D63" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E63" s="10"/>
-      <c r="F63" s="11"/>
+      <c r="E63" s="10" t="n">
+        <v>46247</v>
+      </c>
+      <c r="F63" s="11" t="s">
+        <v>79</v>
+      </c>
       <c r="G63" s="8"/>
       <c r="H63" s="8"/>
-      <c r="I63" s="11"/>
-      <c r="J63" s="12"/>
-      <c r="K63" s="10"/>
+      <c r="I63" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="J63" s="12" t="n">
+        <v>46247</v>
+      </c>
+      <c r="K63" s="10" t="n">
+        <f aca="false">IF(J63="","",J63+14)</f>
+        <v>46261</v>
+      </c>
       <c r="L63" s="11"/>
       <c r="M63" s="8"/>
     </row>
@@ -2883,7 +2895,10 @@
       <c r="H64" s="8"/>
       <c r="I64" s="11"/>
       <c r="J64" s="12"/>
-      <c r="K64" s="10"/>
+      <c r="K64" s="10" t="str">
+        <f aca="false">IF(J64="","",J64+14)</f>
+        <v/>
+      </c>
       <c r="L64" s="11"/>
       <c r="M64" s="8"/>
     </row>
@@ -5256,7 +5271,7 @@
       </c>
       <c r="B5" s="17" t="n">
         <f aca="false">COUNTIF(Tracker!I2:I151,"Solved with Help")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5274,7 +5289,7 @@
       </c>
       <c r="B7" s="17" t="n">
         <f aca="false">COUNTA(Tracker!C2:C151)-COUNTIF(Tracker!I2:I151,"Solved")-COUNTIF(Tracker!I2:I151,"Solved with Help")-COUNTIF(Tracker!I2:I151,"Attempted")</f>
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5283,7 +5298,7 @@
       </c>
       <c r="B8" s="18" t="n">
         <f aca="false">(COUNTIF(Tracker!I2:I151,"Solved")+COUNTIF(Tracker!I2:I151,"Solved with Help"))/COUNTA(Tracker!C2:C151)</f>
-        <v>0.0533333333333333</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5292,7 +5307,7 @@
       </c>
       <c r="B9" s="17" t="n">
         <f aca="true">COUNTIFS(Tracker!K2:K151,"&lt;="&amp;TODAY(),Tracker!K2:K151,"&lt;&gt;",Tracker!L2:L151,"&lt;&gt;Yes")</f>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/neetcode_150_tracker.xlsx
+++ b/neetcode_150_tracker.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="203">
   <si>
     <t xml:space="preserve">#</t>
   </si>
@@ -2889,15 +2889,23 @@
       <c r="D64" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E64" s="10"/>
-      <c r="F64" s="11"/>
+      <c r="E64" s="10" t="n">
+        <v>46249</v>
+      </c>
+      <c r="F64" s="11" t="s">
+        <v>79</v>
+      </c>
       <c r="G64" s="8"/>
       <c r="H64" s="8"/>
-      <c r="I64" s="11"/>
-      <c r="J64" s="12"/>
-      <c r="K64" s="10" t="str">
+      <c r="I64" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="J64" s="12" t="n">
+        <v>46249</v>
+      </c>
+      <c r="K64" s="10" t="n">
         <f aca="false">IF(J64="","",J64+14)</f>
-        <v/>
+        <v>46263</v>
       </c>
       <c r="L64" s="11"/>
       <c r="M64" s="8"/>
@@ -5271,7 +5279,7 @@
       </c>
       <c r="B5" s="17" t="n">
         <f aca="false">COUNTIF(Tracker!I2:I151,"Solved with Help")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5289,7 +5297,7 @@
       </c>
       <c r="B7" s="17" t="n">
         <f aca="false">COUNTA(Tracker!C2:C151)-COUNTIF(Tracker!I2:I151,"Solved")-COUNTIF(Tracker!I2:I151,"Solved with Help")-COUNTIF(Tracker!I2:I151,"Attempted")</f>
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5298,7 +5306,7 @@
       </c>
       <c r="B8" s="18" t="n">
         <f aca="false">(COUNTIF(Tracker!I2:I151,"Solved")+COUNTIF(Tracker!I2:I151,"Solved with Help"))/COUNTA(Tracker!C2:C151)</f>
-        <v>0.06</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/neetcode_150_tracker.xlsx
+++ b/neetcode_150_tracker.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="203">
   <si>
     <t xml:space="preserve">#</t>
   </si>
@@ -272,85 +272,85 @@
     <t xml:space="preserve">Binary Tree Maximum Path Sum</t>
   </si>
   <si>
+    <t xml:space="preserve">Serialize and Deserialize Binary Tree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implement Trie (Prefix Tree)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design Add and Search Words Data Structure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Word Search II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heap / Priority Queue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kth Largest Element in a Stream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Last Stone Weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K Closest Points to Origin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kth Largest Element in an Array</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Task Scheduler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design Twitter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Find Median from Data Stream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backtracking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subsets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Combination Sum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Permutations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subsets II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Combination Sum II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Word Search</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palindrome Partitioning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Letter Combinations of a Phone Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-Queens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Graphs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Islands</t>
+  </si>
+  <si>
     <t xml:space="preserve">Solved with Help</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Serialize and Deserialize Binary Tree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implement Trie (Prefix Tree)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design Add and Search Words Data Structure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Word Search II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heap / Priority Queue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kth Largest Element in a Stream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Last Stone Weight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K Closest Points to Origin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kth Largest Element in an Array</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task Scheduler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design Twitter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Find Median from Data Stream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backtracking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subsets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Combination Sum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Permutations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subsets II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Combination Sum II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Word Search</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palindrome Partitioning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Letter Combinations of a Phone Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-Queens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Graphs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of Islands</t>
   </si>
   <si>
     <t xml:space="preserve">Clone Graph</t>
@@ -2764,14 +2764,12 @@
       <c r="G60" s="8"/>
       <c r="H60" s="8"/>
       <c r="I60" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="J60" s="12" t="n">
-        <v>46217</v>
-      </c>
-      <c r="K60" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="J60" s="12"/>
+      <c r="K60" s="10" t="str">
         <f aca="false">IF(J60="","",J60+14)</f>
-        <v>46231</v>
+        <v/>
       </c>
       <c r="L60" s="11"/>
       <c r="M60" s="8"/>
@@ -2784,7 +2782,7 @@
         <v>66</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D61" s="14" t="s">
         <v>31</v>
@@ -2793,7 +2791,7 @@
         <v>46218</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G61" s="8"/>
       <c r="H61" s="8"/>
@@ -2813,10 +2811,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C62" s="8" t="s">
         <v>86</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>87</v>
       </c>
       <c r="D62" s="13" t="s">
         <v>19</v>
@@ -2830,14 +2828,12 @@
       <c r="G62" s="8"/>
       <c r="H62" s="8"/>
       <c r="I62" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="J62" s="12" t="n">
-        <v>46221</v>
-      </c>
-      <c r="K62" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="J62" s="12"/>
+      <c r="K62" s="10" t="str">
         <f aca="false">IF(J62="","",J62+14)</f>
-        <v>46235</v>
+        <v/>
       </c>
       <c r="L62" s="11"/>
       <c r="M62" s="8"/>
@@ -2847,10 +2843,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D63" s="13" t="s">
         <v>19</v>
@@ -2864,14 +2860,12 @@
       <c r="G63" s="8"/>
       <c r="H63" s="8"/>
       <c r="I63" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="J63" s="12" t="n">
-        <v>46247</v>
-      </c>
-      <c r="K63" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="J63" s="12"/>
+      <c r="K63" s="10" t="str">
         <f aca="false">IF(J63="","",J63+14)</f>
-        <v>46261</v>
+        <v/>
       </c>
       <c r="L63" s="11"/>
       <c r="M63" s="8"/>
@@ -2881,10 +2875,10 @@
         <v>63</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D64" s="14" t="s">
         <v>31</v>
@@ -2898,14 +2892,12 @@
       <c r="G64" s="8"/>
       <c r="H64" s="8"/>
       <c r="I64" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="J64" s="12" t="n">
-        <v>46249</v>
-      </c>
-      <c r="K64" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="J64" s="12"/>
+      <c r="K64" s="10" t="str">
         <f aca="false">IF(J64="","",J64+14)</f>
-        <v>46263</v>
+        <v/>
       </c>
       <c r="L64" s="11"/>
       <c r="M64" s="8"/>
@@ -2915,10 +2907,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C65" s="8" t="s">
         <v>90</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>91</v>
       </c>
       <c r="D65" s="9" t="s">
         <v>15</v>
@@ -2941,10 +2933,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D66" s="9" t="s">
         <v>15</v>
@@ -2967,10 +2959,10 @@
         <v>66</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D67" s="13" t="s">
         <v>19</v>
@@ -2993,10 +2985,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D68" s="13" t="s">
         <v>19</v>
@@ -3019,10 +3011,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D69" s="13" t="s">
         <v>19</v>
@@ -3045,10 +3037,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D70" s="13" t="s">
         <v>19</v>
@@ -3071,10 +3063,10 @@
         <v>70</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D71" s="14" t="s">
         <v>31</v>
@@ -3103,10 +3095,10 @@
         <v>71</v>
       </c>
       <c r="B72" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C72" s="8" t="s">
         <v>98</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>99</v>
       </c>
       <c r="D72" s="13" t="s">
         <v>19</v>
@@ -3129,10 +3121,10 @@
         <v>72</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D73" s="13" t="s">
         <v>19</v>
@@ -3148,12 +3140,10 @@
       <c r="I73" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="J73" s="12" t="n">
-        <v>46221</v>
-      </c>
-      <c r="K73" s="10" t="n">
+      <c r="J73" s="12"/>
+      <c r="K73" s="10" t="str">
         <f aca="false">IF(J73="","",J73+14)</f>
-        <v>46235</v>
+        <v/>
       </c>
       <c r="L73" s="11"/>
       <c r="M73" s="8"/>
@@ -3163,10 +3153,10 @@
         <v>73</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D74" s="13" t="s">
         <v>19</v>
@@ -3189,10 +3179,10 @@
         <v>74</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D75" s="13" t="s">
         <v>19</v>
@@ -3215,10 +3205,10 @@
         <v>75</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D76" s="13" t="s">
         <v>19</v>
@@ -3241,10 +3231,10 @@
         <v>76</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D77" s="13" t="s">
         <v>19</v>
@@ -3258,14 +3248,12 @@
       <c r="G77" s="8"/>
       <c r="H77" s="8"/>
       <c r="I77" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="J77" s="12" t="n">
-        <v>46231</v>
-      </c>
-      <c r="K77" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="J77" s="12"/>
+      <c r="K77" s="10" t="str">
         <f aca="false">IF(J77="","",J77+14)</f>
-        <v>46245</v>
+        <v/>
       </c>
       <c r="L77" s="11"/>
       <c r="M77" s="8"/>
@@ -3275,10 +3263,10 @@
         <v>77</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D78" s="13" t="s">
         <v>19</v>
@@ -3301,10 +3289,10 @@
         <v>78</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D79" s="13" t="s">
         <v>19</v>
@@ -3327,10 +3315,10 @@
         <v>79</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D80" s="14" t="s">
         <v>31</v>
@@ -3353,23 +3341,31 @@
         <v>80</v>
       </c>
       <c r="B81" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C81" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="C81" s="8" t="s">
-        <v>109</v>
-      </c>
       <c r="D81" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E81" s="10"/>
-      <c r="F81" s="11"/>
+      <c r="E81" s="10" t="n">
+        <v>46257</v>
+      </c>
+      <c r="F81" s="11" t="s">
+        <v>79</v>
+      </c>
       <c r="G81" s="8"/>
       <c r="H81" s="8"/>
-      <c r="I81" s="11"/>
-      <c r="J81" s="12"/>
-      <c r="K81" s="10" t="str">
+      <c r="I81" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="J81" s="12" t="n">
+        <v>46257</v>
+      </c>
+      <c r="K81" s="10" t="n">
         <f aca="false">IF(J81="","",J81+14)</f>
-        <v/>
+        <v>46271</v>
       </c>
       <c r="L81" s="11"/>
       <c r="M81" s="8"/>
@@ -3379,7 +3375,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C82" s="8" t="s">
         <v>110</v>
@@ -3405,7 +3401,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C83" s="8" t="s">
         <v>111</v>
@@ -3431,7 +3427,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>112</v>
@@ -3457,7 +3453,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>113</v>
@@ -3483,7 +3479,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C86" s="8" t="s">
         <v>114</v>
@@ -3509,7 +3505,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C87" s="8" t="s">
         <v>115</v>
@@ -3535,7 +3531,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C88" s="8" t="s">
         <v>116</v>
@@ -3561,7 +3557,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C89" s="8" t="s">
         <v>117</v>
@@ -3587,7 +3583,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C90" s="8" t="s">
         <v>118</v>
@@ -3613,7 +3609,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C91" s="8" t="s">
         <v>119</v>
@@ -3639,7 +3635,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C92" s="8" t="s">
         <v>120</v>
@@ -3665,7 +3661,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>121</v>
@@ -5270,16 +5266,16 @@
       </c>
       <c r="B4" s="17" t="n">
         <f aca="false">COUNTIF(Tracker!I2:I151,"Solved")</f>
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="B5" s="17" t="n">
         <f aca="false">COUNTIF(Tracker!I2:I151,"Solved with Help")</f>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5297,7 +5293,7 @@
       </c>
       <c r="B7" s="17" t="n">
         <f aca="false">COUNTA(Tracker!C2:C151)-COUNTIF(Tracker!I2:I151,"Solved")-COUNTIF(Tracker!I2:I151,"Solved with Help")-COUNTIF(Tracker!I2:I151,"Attempted")</f>
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5306,7 +5302,7 @@
       </c>
       <c r="B8" s="18" t="n">
         <f aca="false">(COUNTIF(Tracker!I2:I151,"Solved")+COUNTIF(Tracker!I2:I151,"Solved with Help"))/COUNTA(Tracker!C2:C151)</f>
-        <v>0.0666666666666667</v>
+        <v>0.0733333333333333</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5315,7 +5311,7 @@
       </c>
       <c r="B9" s="17" t="n">
         <f aca="true">COUNTIFS(Tracker!K2:K151,"&lt;="&amp;TODAY(),Tracker!K2:K151,"&lt;&gt;",Tracker!L2:L151,"&lt;&gt;Yes")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5338,7 +5334,7 @@
       </c>
       <c r="B13" s="17" t="str">
         <f aca="false">COUNTIFS(Tracker!D2:D151,"Medium",Tracker!I2:I151,"Solved")&amp;"/"&amp;COUNTIF(Tracker!D2:D151,"Medium")</f>
-        <v>3/101</v>
+        <v>6/101</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5347,7 +5343,7 @@
       </c>
       <c r="B14" s="17" t="str">
         <f aca="false">COUNTIFS(Tracker!D2:D151,"Hard",Tracker!I2:I151,"Solved")&amp;"/"&amp;COUNTIF(Tracker!D2:D151,"Hard")</f>
-        <v>2/21</v>
+        <v>4/21</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
